--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,155 +656,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>24200</v>
+        <v>25100</v>
       </c>
       <c r="E8" s="3">
-        <v>21000</v>
+        <v>21900</v>
       </c>
       <c r="F8" s="3">
-        <v>22900</v>
+        <v>23600</v>
       </c>
       <c r="G8" s="3">
-        <v>21100</v>
+        <v>20500</v>
       </c>
       <c r="H8" s="3">
+        <v>22400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K8" s="3">
+        <v>19300</v>
+      </c>
+      <c r="L8" s="3">
+        <v>23700</v>
+      </c>
+      <c r="M8" s="3">
+        <v>24900</v>
+      </c>
+      <c r="N8" s="3">
+        <v>24100</v>
+      </c>
+      <c r="O8" s="3">
+        <v>19600</v>
+      </c>
+      <c r="P8" s="3">
+        <v>46000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>16900</v>
+      </c>
+      <c r="R8" s="3">
         <v>20500</v>
       </c>
-      <c r="I8" s="3">
-        <v>19300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>23700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>24900</v>
-      </c>
-      <c r="L8" s="3">
-        <v>24100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>19600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>46000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>16900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>20500</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>38000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -862,8 +875,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -921,8 +940,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,8 +969,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1003,8 +1030,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,8 +1095,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1121,67 +1160,79 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>900</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>900</v>
       </c>
       <c r="G15" s="3">
+        <v>900</v>
+      </c>
+      <c r="H15" s="3">
+        <v>900</v>
+      </c>
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
-        <v>800</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
       <c r="L15" s="3">
+        <v>800</v>
+      </c>
+      <c r="M15" s="3">
         <v>700</v>
       </c>
-      <c r="M15" s="3">
-        <v>600</v>
-      </c>
       <c r="N15" s="3">
-        <v>1900</v>
+        <v>700</v>
       </c>
       <c r="O15" s="3">
         <v>600</v>
       </c>
       <c r="P15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>600</v>
+      </c>
+      <c r="R15" s="3">
         <v>800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2400</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,67 +1251,75 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13400</v>
+        <v>14300</v>
       </c>
       <c r="E17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>10800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K17" s="3">
         <v>11100</v>
       </c>
-      <c r="F17" s="3">
-        <v>12700</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="L17" s="3">
         <v>12300</v>
       </c>
-      <c r="H17" s="3">
-        <v>11100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>11100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>12300</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>16500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>15600</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1268,58 +1327,64 @@
         <v>10800</v>
       </c>
       <c r="E18" s="3">
-        <v>9900</v>
+        <v>9500</v>
       </c>
       <c r="F18" s="3">
-        <v>10300</v>
+        <v>10600</v>
       </c>
       <c r="G18" s="3">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="H18" s="3">
-        <v>9400</v>
+        <v>10000</v>
       </c>
       <c r="I18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="K18" s="3">
         <v>8300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>11400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>13300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>13000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>12100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>29500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>11200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>22400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,131 +1406,145 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>10900</v>
+        <v>4900</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="F20" s="3">
-        <v>5900</v>
+        <v>10700</v>
       </c>
       <c r="G20" s="3">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>3000</v>
+        <v>5800</v>
       </c>
       <c r="I20" s="3">
-        <v>4000</v>
+        <v>7900</v>
       </c>
       <c r="J20" s="3">
         <v>2900</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="L20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>3200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>22700</v>
+        <v>16700</v>
       </c>
       <c r="E21" s="3">
-        <v>10900</v>
+        <v>10100</v>
       </c>
       <c r="F21" s="3">
-        <v>17100</v>
+        <v>22100</v>
       </c>
       <c r="G21" s="3">
-        <v>17800</v>
+        <v>10600</v>
       </c>
       <c r="H21" s="3">
-        <v>13200</v>
+        <v>16700</v>
       </c>
       <c r="I21" s="3">
+        <v>17300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K21" s="3">
         <v>13000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>15000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>14000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>13500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>32500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>15500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>28000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>500</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
         <v>500</v>
@@ -1477,16 +1556,16 @@
         <v>500</v>
       </c>
       <c r="H22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>500</v>
       </c>
       <c r="J22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L22" s="3">
         <v>600</v>
@@ -1495,149 +1574,167 @@
         <v>600</v>
       </c>
       <c r="N22" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="O22" s="3">
         <v>600</v>
       </c>
       <c r="P22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
+        <v>600</v>
+      </c>
+      <c r="S22" s="3">
         <v>1700</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>21300</v>
+        <v>15700</v>
       </c>
       <c r="E23" s="3">
-        <v>9400</v>
+        <v>8500</v>
       </c>
       <c r="F23" s="3">
-        <v>15700</v>
+        <v>20700</v>
       </c>
       <c r="G23" s="3">
-        <v>16500</v>
+        <v>9100</v>
       </c>
       <c r="H23" s="3">
-        <v>11900</v>
+        <v>15300</v>
       </c>
       <c r="I23" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K23" s="3">
         <v>11700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>13700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>12700</v>
       </c>
       <c r="L23" s="3">
         <v>13700</v>
       </c>
       <c r="M23" s="3">
+        <v>12700</v>
+      </c>
+      <c r="N23" s="3">
+        <v>13700</v>
+      </c>
+      <c r="O23" s="3">
         <v>12200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>28800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>11200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>14000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>23800</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>5000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,126 +1792,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>18800</v>
+        <v>12700</v>
       </c>
       <c r="E26" s="3">
-        <v>6700</v>
+        <v>6400</v>
       </c>
       <c r="F26" s="3">
-        <v>12000</v>
+        <v>18300</v>
       </c>
       <c r="G26" s="3">
-        <v>14200</v>
+        <v>6600</v>
       </c>
       <c r="H26" s="3">
-        <v>9500</v>
+        <v>11700</v>
       </c>
       <c r="I26" s="3">
+        <v>13900</v>
+      </c>
+      <c r="J26" s="3">
         <v>9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L26" s="3">
         <v>11600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>10400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>10800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>9800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>22900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>11800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>18900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>18900</v>
+        <v>12900</v>
       </c>
       <c r="E27" s="3">
-        <v>6700</v>
+        <v>6400</v>
       </c>
       <c r="F27" s="3">
-        <v>12000</v>
+        <v>18400</v>
       </c>
       <c r="G27" s="3">
-        <v>14200</v>
+        <v>6600</v>
       </c>
       <c r="H27" s="3">
-        <v>9500</v>
+        <v>11700</v>
       </c>
       <c r="I27" s="3">
+        <v>13900</v>
+      </c>
+      <c r="J27" s="3">
         <v>9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L27" s="3">
         <v>11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>10400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>10800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>10500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>22400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>8600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>11300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>18500</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1987,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +2052,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2117,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,126 +2182,144 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-10900</v>
+        <v>-4900</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F32" s="3">
-        <v>-5900</v>
+        <v>-10700</v>
       </c>
       <c r="G32" s="3">
-        <v>-8200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-3000</v>
+        <v>-5800</v>
       </c>
       <c r="I32" s="3">
-        <v>-4000</v>
+        <v>-7900</v>
       </c>
       <c r="J32" s="3">
         <v>-2900</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="L32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-3200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>18900</v>
+        <v>12900</v>
       </c>
       <c r="E33" s="3">
-        <v>6700</v>
+        <v>6400</v>
       </c>
       <c r="F33" s="3">
-        <v>12000</v>
+        <v>18400</v>
       </c>
       <c r="G33" s="3">
-        <v>14200</v>
+        <v>6600</v>
       </c>
       <c r="H33" s="3">
-        <v>9500</v>
+        <v>11700</v>
       </c>
       <c r="I33" s="3">
+        <v>13900</v>
+      </c>
+      <c r="J33" s="3">
         <v>9300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L33" s="3">
         <v>11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>10400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>10800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>10500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>22400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>8600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>11300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>18500</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,131 +2377,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>18900</v>
+        <v>12900</v>
       </c>
       <c r="E35" s="3">
-        <v>6700</v>
+        <v>6400</v>
       </c>
       <c r="F35" s="3">
-        <v>12000</v>
+        <v>18400</v>
       </c>
       <c r="G35" s="3">
-        <v>14200</v>
+        <v>6600</v>
       </c>
       <c r="H35" s="3">
-        <v>9500</v>
+        <v>11700</v>
       </c>
       <c r="I35" s="3">
+        <v>13900</v>
+      </c>
+      <c r="J35" s="3">
         <v>9300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L35" s="3">
         <v>11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>10400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>10800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>10500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>22400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>8600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>11300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>18500</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2541,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,50 +2566,52 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6500</v>
+        <v>3200</v>
       </c>
       <c r="E41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N41" s="3">
         <v>4700</v>
       </c>
-      <c r="F41" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>4500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L41" s="3">
-        <v>4700</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,8 +2627,14 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2513,50 +2692,56 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14800</v>
+        <v>21600</v>
       </c>
       <c r="E43" s="3">
-        <v>13100</v>
+        <v>14700</v>
       </c>
       <c r="F43" s="3">
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="G43" s="3">
-        <v>10800</v>
+        <v>12800</v>
       </c>
       <c r="H43" s="3">
-        <v>10600</v>
+        <v>12200</v>
       </c>
       <c r="I43" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K43" s="3">
         <v>9500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>9700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7300</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2757,14 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2631,50 +2822,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>271400</v>
+        <v>367100</v>
       </c>
       <c r="E45" s="3">
-        <v>262300</v>
+        <v>259900</v>
       </c>
       <c r="F45" s="3">
-        <v>281000</v>
+        <v>264500</v>
       </c>
       <c r="G45" s="3">
-        <v>287800</v>
+        <v>255700</v>
       </c>
       <c r="H45" s="3">
-        <v>277400</v>
+        <v>273900</v>
       </c>
       <c r="I45" s="3">
+        <v>280500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>270300</v>
+      </c>
+      <c r="K45" s="3">
         <v>279800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>299800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>292400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>291600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>17000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>21300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,50 +2887,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>292700</v>
+        <v>391900</v>
       </c>
       <c r="E46" s="3">
-        <v>280200</v>
+        <v>282200</v>
       </c>
       <c r="F46" s="3">
-        <v>299700</v>
+        <v>285300</v>
       </c>
       <c r="G46" s="3">
-        <v>301500</v>
+        <v>273100</v>
       </c>
       <c r="H46" s="3">
-        <v>290100</v>
+        <v>292100</v>
       </c>
       <c r="I46" s="3">
+        <v>293800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>282800</v>
+      </c>
+      <c r="K46" s="3">
         <v>291200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>314000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>307500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>308500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>29200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>31300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,50 +2952,56 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="E47" s="3">
-        <v>5500</v>
+        <v>8500</v>
       </c>
       <c r="F47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G47" s="3">
         <v>5400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>5600</v>
       </c>
       <c r="H47" s="3">
         <v>5300</v>
       </c>
       <c r="I47" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K47" s="3">
         <v>6000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>8200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>8000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>11100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>9800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2808,50 +3017,56 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15700</v>
+        <v>14500</v>
       </c>
       <c r="E48" s="3">
-        <v>16400</v>
+        <v>14700</v>
       </c>
       <c r="F48" s="3">
+        <v>15300</v>
+      </c>
+      <c r="G48" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="L48" s="3">
         <v>17200</v>
       </c>
-      <c r="G48" s="3">
-        <v>14800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>16200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>17200</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>20100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>19700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,16 +3082,22 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>39900</v>
+        <v>43000</v>
       </c>
       <c r="E49" s="3">
-        <v>39400</v>
+        <v>41300</v>
       </c>
       <c r="F49" s="3">
         <v>38900</v>
@@ -2885,13 +3106,13 @@
         <v>38400</v>
       </c>
       <c r="H49" s="3">
+        <v>37900</v>
+      </c>
+      <c r="I49" s="3">
+        <v>37400</v>
+      </c>
+      <c r="J49" s="3">
         <v>300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>200</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -2900,17 +3121,17 @@
         <v>200</v>
       </c>
       <c r="M49" s="3">
+        <v>200</v>
+      </c>
+      <c r="N49" s="3">
+        <v>200</v>
+      </c>
+      <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3147,14 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3212,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,50 +3277,56 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2400</v>
+        <v>6600</v>
       </c>
       <c r="E52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3342,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,50 +3407,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>355500</v>
+        <v>460900</v>
       </c>
       <c r="E54" s="3">
-        <v>343800</v>
+        <v>349200</v>
       </c>
       <c r="F54" s="3">
-        <v>363300</v>
+        <v>346500</v>
       </c>
       <c r="G54" s="3">
-        <v>362000</v>
+        <v>335100</v>
       </c>
       <c r="H54" s="3">
-        <v>312900</v>
+        <v>354100</v>
       </c>
       <c r="I54" s="3">
+        <v>352900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>305000</v>
+      </c>
+      <c r="K54" s="3">
         <v>315300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>338700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>337400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>338400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>61500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>62500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3472,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3501,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,8 +3526,10 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3276,41 +3537,41 @@
         <v>1600</v>
       </c>
       <c r="E57" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="F57" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="G57" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="H57" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="I57" s="3">
         <v>1500</v>
       </c>
       <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>23700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,50 +3587,56 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9600</v>
+        <v>20300</v>
       </c>
       <c r="E58" s="3">
-        <v>7100</v>
+        <v>18100</v>
       </c>
       <c r="F58" s="3">
-        <v>7700</v>
+        <v>9300</v>
       </c>
       <c r="G58" s="3">
-        <v>6700</v>
+        <v>7000</v>
       </c>
       <c r="H58" s="3">
-        <v>4800</v>
+        <v>7500</v>
       </c>
       <c r="I58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J58" s="3">
         <v>4700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L58" s="3">
         <v>4600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,50 +3652,56 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>14400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>22100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>20500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>26700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>24800</v>
+      </c>
+      <c r="N59" s="3">
         <v>14800</v>
       </c>
-      <c r="E59" s="3">
-        <v>12000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>22600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>21100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>12800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>11800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>26700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>24800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>14800</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>13200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,50 +3717,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>26000</v>
+        <v>47200</v>
       </c>
       <c r="E60" s="3">
-        <v>20600</v>
+        <v>40800</v>
       </c>
       <c r="F60" s="3">
-        <v>32100</v>
+        <v>25300</v>
       </c>
       <c r="G60" s="3">
-        <v>29300</v>
+        <v>20000</v>
       </c>
       <c r="H60" s="3">
-        <v>19000</v>
+        <v>31200</v>
       </c>
       <c r="I60" s="3">
+        <v>28500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="K60" s="3">
         <v>18000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>33700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>31200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>21600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>39300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>17300</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,50 +3782,56 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>23600</v>
+        <v>118000</v>
       </c>
       <c r="E61" s="3">
-        <v>24500</v>
+        <v>32500</v>
       </c>
       <c r="F61" s="3">
-        <v>27200</v>
+        <v>23000</v>
       </c>
       <c r="G61" s="3">
-        <v>25300</v>
+        <v>23900</v>
       </c>
       <c r="H61" s="3">
-        <v>11500</v>
+        <v>26500</v>
       </c>
       <c r="I61" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K61" s="3">
         <v>12300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>13000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>16200</v>
-      </c>
-      <c r="L61" s="3">
-        <v>16600</v>
       </c>
       <c r="M61" s="3">
         <v>16200</v>
       </c>
       <c r="N61" s="3">
+        <v>16600</v>
+      </c>
+      <c r="O61" s="3">
+        <v>16200</v>
+      </c>
+      <c r="P61" s="3">
         <v>15900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3562,50 +3847,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24900</v>
+        <v>19000</v>
       </c>
       <c r="E62" s="3">
-        <v>22800</v>
+        <v>8800</v>
       </c>
       <c r="F62" s="3">
-        <v>21300</v>
+        <v>24300</v>
       </c>
       <c r="G62" s="3">
-        <v>22800</v>
+        <v>22200</v>
       </c>
       <c r="H62" s="3">
+        <v>20700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>22200</v>
+      </c>
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3912,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3977,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +4042,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,50 +4107,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>75100</v>
+        <v>184500</v>
       </c>
       <c r="E66" s="3">
-        <v>68400</v>
+        <v>82600</v>
       </c>
       <c r="F66" s="3">
-        <v>81100</v>
+        <v>73200</v>
       </c>
       <c r="G66" s="3">
-        <v>77700</v>
+        <v>66700</v>
       </c>
       <c r="H66" s="3">
-        <v>31400</v>
+        <v>79000</v>
       </c>
       <c r="I66" s="3">
+        <v>75800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K66" s="3">
         <v>31300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>47700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>48900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>40000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>57900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>36500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4172,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4201,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4262,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4327,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4392,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,50 +4457,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>23300</v>
+        <v>22300</v>
       </c>
       <c r="E72" s="3">
-        <v>13400</v>
+        <v>18400</v>
       </c>
       <c r="F72" s="3">
-        <v>16700</v>
+        <v>22700</v>
       </c>
       <c r="G72" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H72" s="3">
         <v>16300</v>
       </c>
-      <c r="H72" s="3">
-        <v>12000</v>
-      </c>
       <c r="I72" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K72" s="3">
         <v>12200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>14400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>12600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>20200</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
         <v>22100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4522,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4587,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4652,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,50 +4717,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>280400</v>
+        <v>276400</v>
       </c>
       <c r="E76" s="3">
-        <v>275400</v>
+        <v>266600</v>
       </c>
       <c r="F76" s="3">
-        <v>282200</v>
+        <v>273300</v>
       </c>
       <c r="G76" s="3">
-        <v>284300</v>
+        <v>268400</v>
       </c>
       <c r="H76" s="3">
-        <v>281500</v>
+        <v>275100</v>
       </c>
       <c r="I76" s="3">
+        <v>277100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>274400</v>
+      </c>
+      <c r="K76" s="3">
         <v>284000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>290900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>288500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>298300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>26000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4782,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,131 +4847,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>18900</v>
+        <v>12900</v>
       </c>
       <c r="E81" s="3">
-        <v>6700</v>
+        <v>6400</v>
       </c>
       <c r="F81" s="3">
-        <v>12000</v>
+        <v>18400</v>
       </c>
       <c r="G81" s="3">
-        <v>14200</v>
+        <v>6600</v>
       </c>
       <c r="H81" s="3">
-        <v>9500</v>
+        <v>11700</v>
       </c>
       <c r="I81" s="3">
+        <v>13900</v>
+      </c>
+      <c r="J81" s="3">
         <v>9300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L81" s="3">
         <v>11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>10400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>10800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>10500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>22400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>8600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>11300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>18500</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,67 +5011,75 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="F83" s="3">
         <v>900</v>
       </c>
       <c r="G83" s="3">
+        <v>900</v>
+      </c>
+      <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
-        <v>800</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>800</v>
       </c>
       <c r="M83" s="3">
+        <v>700</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +5137,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +5202,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5267,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5332,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,67 +5397,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>17900</v>
+        <v>14000</v>
       </c>
       <c r="E89" s="3">
-        <v>-2800</v>
+        <v>14100</v>
       </c>
       <c r="F89" s="3">
-        <v>9200</v>
+        <v>17500</v>
       </c>
       <c r="G89" s="3">
-        <v>16000</v>
+        <v>-2700</v>
       </c>
       <c r="H89" s="3">
-        <v>7500</v>
+        <v>9000</v>
       </c>
       <c r="I89" s="3">
+        <v>15600</v>
+      </c>
+      <c r="J89" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-8500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>15300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>23900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>32200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>21400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,67 +5491,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-600</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5617,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,67 +5682,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>8500</v>
+        <v>-2100</v>
       </c>
       <c r="E94" s="3">
-        <v>12100</v>
+        <v>9800</v>
       </c>
       <c r="F94" s="3">
-        <v>14300</v>
+        <v>8200</v>
       </c>
       <c r="G94" s="3">
-        <v>-11000</v>
+        <v>11800</v>
       </c>
       <c r="H94" s="3">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="I94" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K94" s="3">
         <v>13700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>3000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>12700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-6900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,41 +5776,43 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8800</v>
+        <v>-9000</v>
       </c>
       <c r="E96" s="3">
-        <v>-10000</v>
+        <v>-10800</v>
       </c>
       <c r="F96" s="3">
-        <v>-11900</v>
+        <v>-8600</v>
       </c>
       <c r="G96" s="3">
-        <v>-10100</v>
+        <v>-9700</v>
       </c>
       <c r="H96" s="3">
-        <v>-9300</v>
+        <v>-11600</v>
       </c>
       <c r="I96" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-12100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-10500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-17900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5370,8 +5837,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5902,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5967,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,181 +6032,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-15100</v>
+        <v>83700</v>
       </c>
       <c r="E100" s="3">
-        <v>-16200</v>
+        <v>-18200</v>
       </c>
       <c r="F100" s="3">
-        <v>-15700</v>
+        <v>-14700</v>
       </c>
       <c r="G100" s="3">
-        <v>2800</v>
+        <v>-15800</v>
       </c>
       <c r="H100" s="3">
-        <v>-13500</v>
+        <v>-15300</v>
       </c>
       <c r="I100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-17900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-17000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-22000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>-9700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-27800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-16000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>10900</v>
+        <v>95400</v>
       </c>
       <c r="E102" s="3">
-        <v>-7300</v>
+        <v>6100</v>
       </c>
       <c r="F102" s="3">
-        <v>8100</v>
+        <v>10600</v>
       </c>
       <c r="G102" s="3">
-        <v>8100</v>
+        <v>-7100</v>
       </c>
       <c r="H102" s="3">
-        <v>4000</v>
+        <v>7900</v>
       </c>
       <c r="I102" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J102" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-13200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>5100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>17800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,92 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -751,62 +752,65 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>25100</v>
+        <v>20200</v>
       </c>
       <c r="E8" s="3">
-        <v>21900</v>
+        <v>23200</v>
       </c>
       <c r="F8" s="3">
-        <v>23600</v>
+        <v>20200</v>
       </c>
       <c r="G8" s="3">
-        <v>20500</v>
+        <v>21700</v>
       </c>
       <c r="H8" s="3">
-        <v>22400</v>
+        <v>18900</v>
       </c>
       <c r="I8" s="3">
         <v>20600</v>
       </c>
       <c r="J8" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K8" s="3">
         <v>20000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,8 +820,11 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -881,8 +888,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -946,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,8 +984,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1036,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,8 +1118,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1166,25 +1186,28 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I15" s="3">
         <v>800</v>
@@ -1196,32 +1219,32 @@
         <v>700</v>
       </c>
       <c r="L15" s="3">
+        <v>700</v>
+      </c>
+      <c r="M15" s="3">
         <v>800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>700</v>
       </c>
       <c r="O15" s="3">
+        <v>700</v>
+      </c>
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,8 +1254,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1253,62 +1279,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14300</v>
+        <v>11400</v>
       </c>
       <c r="E17" s="3">
-        <v>12400</v>
+        <v>13200</v>
       </c>
       <c r="F17" s="3">
-        <v>13000</v>
+        <v>11400</v>
       </c>
       <c r="G17" s="3">
+        <v>12000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K17" s="3">
         <v>10800</v>
       </c>
-      <c r="H17" s="3">
-        <v>12400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>12000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>10800</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,62 +1345,65 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10800</v>
+        <v>8800</v>
       </c>
       <c r="E18" s="3">
-        <v>9500</v>
+        <v>10000</v>
       </c>
       <c r="F18" s="3">
-        <v>10600</v>
+        <v>8800</v>
       </c>
       <c r="G18" s="3">
         <v>9700</v>
       </c>
       <c r="H18" s="3">
-        <v>10000</v>
+        <v>8900</v>
       </c>
       <c r="I18" s="3">
-        <v>8600</v>
+        <v>9200</v>
       </c>
       <c r="J18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K18" s="3">
         <v>9200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>29500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1408,62 +1441,63 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
-        <v>-600</v>
-      </c>
       <c r="F20" s="3">
-        <v>10700</v>
+        <v>-500</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="H20" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>7900</v>
+        <v>5300</v>
       </c>
       <c r="J20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1473,62 +1507,65 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>16700</v>
+        <v>14600</v>
       </c>
       <c r="E21" s="3">
-        <v>10100</v>
+        <v>15800</v>
       </c>
       <c r="F21" s="3">
-        <v>22100</v>
+        <v>9300</v>
       </c>
       <c r="G21" s="3">
-        <v>10600</v>
+        <v>20400</v>
       </c>
       <c r="H21" s="3">
-        <v>16700</v>
+        <v>9800</v>
       </c>
       <c r="I21" s="3">
-        <v>17300</v>
+        <v>15400</v>
       </c>
       <c r="J21" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K21" s="3">
         <v>12900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>13500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>32500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>15500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,37 +1575,40 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>3200</v>
       </c>
       <c r="E22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>500</v>
       </c>
       <c r="H22" s="3">
+        <v>500</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
-        <v>500</v>
-      </c>
       <c r="J22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
       </c>
       <c r="L22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M22" s="3">
         <v>600</v>
@@ -1580,20 +1620,20 @@
         <v>600</v>
       </c>
       <c r="P22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>600</v>
       </c>
       <c r="R22" s="3">
         <v>600</v>
       </c>
       <c r="S22" s="3">
+        <v>600</v>
+      </c>
+      <c r="T22" s="3">
         <v>1700</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1603,62 +1643,65 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>15700</v>
+        <v>10400</v>
       </c>
       <c r="E23" s="3">
-        <v>8500</v>
+        <v>14500</v>
       </c>
       <c r="F23" s="3">
-        <v>20700</v>
+        <v>7800</v>
       </c>
       <c r="G23" s="3">
-        <v>9100</v>
+        <v>19100</v>
       </c>
       <c r="H23" s="3">
-        <v>15300</v>
+        <v>8400</v>
       </c>
       <c r="I23" s="3">
-        <v>16100</v>
+        <v>14100</v>
       </c>
       <c r="J23" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K23" s="3">
         <v>11600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>28800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>23800</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,62 +1711,65 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>2200</v>
       </c>
       <c r="R24" s="3">
         <v>2200</v>
       </c>
       <c r="S24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T24" s="3">
         <v>5000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1733,8 +1779,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,62 +1847,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>12700</v>
+        <v>8400</v>
       </c>
       <c r="E26" s="3">
-        <v>6400</v>
+        <v>11700</v>
       </c>
       <c r="F26" s="3">
-        <v>18300</v>
+        <v>5900</v>
       </c>
       <c r="G26" s="3">
-        <v>6600</v>
+        <v>16900</v>
       </c>
       <c r="H26" s="3">
-        <v>11700</v>
+        <v>6000</v>
       </c>
       <c r="I26" s="3">
-        <v>13900</v>
+        <v>10800</v>
       </c>
       <c r="J26" s="3">
-        <v>9300</v>
+        <v>12800</v>
       </c>
       <c r="K26" s="3">
         <v>9300</v>
       </c>
       <c r="L26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M26" s="3">
         <v>11600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>22900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,62 +1915,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12900</v>
+        <v>8500</v>
       </c>
       <c r="E27" s="3">
-        <v>6400</v>
+        <v>11800</v>
       </c>
       <c r="F27" s="3">
-        <v>18400</v>
+        <v>5900</v>
       </c>
       <c r="G27" s="3">
-        <v>6600</v>
+        <v>17000</v>
       </c>
       <c r="H27" s="3">
-        <v>11700</v>
+        <v>6000</v>
       </c>
       <c r="I27" s="3">
-        <v>13900</v>
+        <v>10800</v>
       </c>
       <c r="J27" s="3">
-        <v>9300</v>
+        <v>12800</v>
       </c>
       <c r="K27" s="3">
         <v>9300</v>
       </c>
       <c r="L27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M27" s="3">
         <v>11600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>22400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1993,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2058,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2123,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2188,62 +2255,65 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
-        <v>600</v>
-      </c>
       <c r="F32" s="3">
-        <v>-10700</v>
+        <v>500</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-9800</v>
       </c>
       <c r="H32" s="3">
-        <v>-5800</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-7900</v>
+        <v>-5300</v>
       </c>
       <c r="J32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2253,62 +2323,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12900</v>
+        <v>8500</v>
       </c>
       <c r="E33" s="3">
-        <v>6400</v>
+        <v>11800</v>
       </c>
       <c r="F33" s="3">
-        <v>18400</v>
+        <v>5900</v>
       </c>
       <c r="G33" s="3">
-        <v>6600</v>
+        <v>17000</v>
       </c>
       <c r="H33" s="3">
-        <v>11700</v>
+        <v>6000</v>
       </c>
       <c r="I33" s="3">
-        <v>13900</v>
+        <v>10800</v>
       </c>
       <c r="J33" s="3">
-        <v>9300</v>
+        <v>12800</v>
       </c>
       <c r="K33" s="3">
         <v>9300</v>
       </c>
       <c r="L33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M33" s="3">
         <v>11600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>22400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2318,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2383,62 +2459,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12900</v>
+        <v>8500</v>
       </c>
       <c r="E35" s="3">
-        <v>6400</v>
+        <v>11800</v>
       </c>
       <c r="F35" s="3">
-        <v>18400</v>
+        <v>5900</v>
       </c>
       <c r="G35" s="3">
-        <v>6600</v>
+        <v>17000</v>
       </c>
       <c r="H35" s="3">
-        <v>11700</v>
+        <v>6000</v>
       </c>
       <c r="I35" s="3">
-        <v>13900</v>
+        <v>10800</v>
       </c>
       <c r="J35" s="3">
-        <v>9300</v>
+        <v>12800</v>
       </c>
       <c r="K35" s="3">
         <v>9300</v>
       </c>
       <c r="L35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M35" s="3">
         <v>11600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>22400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,67 +2527,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2568,53 +2654,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3200</v>
+        <v>8500</v>
       </c>
       <c r="E41" s="3">
-        <v>7600</v>
+        <v>2900</v>
       </c>
       <c r="F41" s="3">
-        <v>6300</v>
+        <v>7000</v>
       </c>
       <c r="G41" s="3">
-        <v>4600</v>
+        <v>5800</v>
       </c>
       <c r="H41" s="3">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="I41" s="3">
-        <v>2800</v>
+        <v>5600</v>
       </c>
       <c r="J41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2633,8 +2720,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2698,53 +2788,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>21600</v>
+        <v>17500</v>
       </c>
       <c r="E43" s="3">
-        <v>14700</v>
+        <v>19900</v>
       </c>
       <c r="F43" s="3">
-        <v>14500</v>
+        <v>13500</v>
       </c>
       <c r="G43" s="3">
-        <v>12800</v>
+        <v>13300</v>
       </c>
       <c r="H43" s="3">
-        <v>12200</v>
+        <v>11800</v>
       </c>
       <c r="I43" s="3">
-        <v>10500</v>
+        <v>11200</v>
       </c>
       <c r="J43" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K43" s="3">
         <v>10300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>9800</v>
       </c>
       <c r="M43" s="3">
         <v>9800</v>
       </c>
       <c r="N43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O43" s="3">
         <v>12200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,8 +2856,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2828,53 +2924,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>367100</v>
+        <v>320200</v>
       </c>
       <c r="E45" s="3">
-        <v>259900</v>
+        <v>338500</v>
       </c>
       <c r="F45" s="3">
-        <v>264500</v>
+        <v>239600</v>
       </c>
       <c r="G45" s="3">
-        <v>255700</v>
+        <v>243900</v>
       </c>
       <c r="H45" s="3">
-        <v>273900</v>
+        <v>235700</v>
       </c>
       <c r="I45" s="3">
-        <v>280500</v>
+        <v>252500</v>
       </c>
       <c r="J45" s="3">
+        <v>258600</v>
+      </c>
+      <c r="K45" s="3">
         <v>270300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>279800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>299800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>292400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>291600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,53 +2992,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>391900</v>
+        <v>346200</v>
       </c>
       <c r="E46" s="3">
-        <v>282200</v>
+        <v>361300</v>
       </c>
       <c r="F46" s="3">
-        <v>285300</v>
+        <v>260100</v>
       </c>
       <c r="G46" s="3">
-        <v>273100</v>
+        <v>263000</v>
       </c>
       <c r="H46" s="3">
-        <v>292100</v>
+        <v>251700</v>
       </c>
       <c r="I46" s="3">
-        <v>293800</v>
+        <v>269300</v>
       </c>
       <c r="J46" s="3">
+        <v>270900</v>
+      </c>
+      <c r="K46" s="3">
         <v>282800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>291200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>314000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>307500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>308500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,53 +3060,56 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4800</v>
+        <v>14000</v>
       </c>
       <c r="E47" s="3">
-        <v>8500</v>
+        <v>4500</v>
       </c>
       <c r="F47" s="3">
-        <v>4700</v>
+        <v>7800</v>
       </c>
       <c r="G47" s="3">
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="H47" s="3">
-        <v>5300</v>
+        <v>5000</v>
       </c>
       <c r="I47" s="3">
-        <v>5500</v>
+        <v>4900</v>
       </c>
       <c r="J47" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K47" s="3">
         <v>5200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3023,52 +3128,55 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14500</v>
+        <v>12700</v>
       </c>
       <c r="E48" s="3">
-        <v>14700</v>
+        <v>13400</v>
       </c>
       <c r="F48" s="3">
-        <v>15300</v>
+        <v>13500</v>
       </c>
       <c r="G48" s="3">
-        <v>16000</v>
+        <v>14100</v>
       </c>
       <c r="H48" s="3">
-        <v>16700</v>
+        <v>14800</v>
       </c>
       <c r="I48" s="3">
-        <v>14500</v>
+        <v>15400</v>
       </c>
       <c r="J48" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K48" s="3">
         <v>15200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20600</v>
-      </c>
-      <c r="O48" s="3">
-        <v>19700</v>
       </c>
       <c r="P48" s="3">
         <v>19700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>19700</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -3088,34 +3196,37 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>43000</v>
+        <v>39800</v>
       </c>
       <c r="E49" s="3">
-        <v>41300</v>
+        <v>39700</v>
       </c>
       <c r="F49" s="3">
-        <v>38900</v>
+        <v>38100</v>
       </c>
       <c r="G49" s="3">
-        <v>38400</v>
+        <v>35800</v>
       </c>
       <c r="H49" s="3">
-        <v>37900</v>
+        <v>35400</v>
       </c>
       <c r="I49" s="3">
-        <v>37400</v>
+        <v>35000</v>
       </c>
       <c r="J49" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K49" s="3">
         <v>300</v>
-      </c>
-      <c r="K49" s="3">
-        <v>200</v>
       </c>
       <c r="L49" s="3">
         <v>200</v>
@@ -3127,13 +3238,13 @@
         <v>200</v>
       </c>
       <c r="O49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P49" s="3">
         <v>300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>300</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3153,8 +3264,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3218,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3283,8 +3400,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3292,7 +3412,7 @@
         <v>6600</v>
       </c>
       <c r="E52" s="3">
-        <v>2500</v>
+        <v>6100</v>
       </c>
       <c r="F52" s="3">
         <v>2300</v>
@@ -3304,7 +3424,7 @@
         <v>2100</v>
       </c>
       <c r="I52" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="J52" s="3">
         <v>1600</v>
@@ -3313,23 +3433,23 @@
         <v>1600</v>
       </c>
       <c r="L52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1100</v>
       </c>
       <c r="O52" s="3">
         <v>1100</v>
       </c>
       <c r="P52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,8 +3468,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3413,53 +3536,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>460900</v>
+        <v>419300</v>
       </c>
       <c r="E54" s="3">
-        <v>349200</v>
+        <v>424900</v>
       </c>
       <c r="F54" s="3">
-        <v>346500</v>
+        <v>321900</v>
       </c>
       <c r="G54" s="3">
-        <v>335100</v>
+        <v>319400</v>
       </c>
       <c r="H54" s="3">
-        <v>354100</v>
+        <v>308900</v>
       </c>
       <c r="I54" s="3">
-        <v>352900</v>
+        <v>326500</v>
       </c>
       <c r="J54" s="3">
+        <v>325300</v>
+      </c>
+      <c r="K54" s="3">
         <v>305000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>315300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>338700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>337400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>338400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>61500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3478,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3503,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3528,53 +3658,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1500</v>
-      </c>
       <c r="J57" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="K57" s="3">
         <v>1500</v>
       </c>
       <c r="L57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>23700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,53 +3724,56 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20300</v>
+        <v>19100</v>
       </c>
       <c r="E58" s="3">
-        <v>18100</v>
+        <v>18700</v>
       </c>
       <c r="F58" s="3">
-        <v>9300</v>
+        <v>16700</v>
       </c>
       <c r="G58" s="3">
-        <v>7000</v>
+        <v>8600</v>
       </c>
       <c r="H58" s="3">
-        <v>7500</v>
+        <v>6400</v>
       </c>
       <c r="I58" s="3">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="J58" s="3">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="K58" s="3">
         <v>4700</v>
       </c>
       <c r="L58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M58" s="3">
         <v>4600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4100</v>
       </c>
       <c r="N58" s="3">
         <v>4100</v>
       </c>
       <c r="O58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P58" s="3">
         <v>3700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,53 +3792,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25300</v>
+        <v>11500</v>
       </c>
       <c r="E59" s="3">
-        <v>21100</v>
+        <v>23300</v>
       </c>
       <c r="F59" s="3">
-        <v>14400</v>
+        <v>19400</v>
       </c>
       <c r="G59" s="3">
-        <v>11700</v>
+        <v>13300</v>
       </c>
       <c r="H59" s="3">
-        <v>22100</v>
+        <v>10800</v>
       </c>
       <c r="I59" s="3">
-        <v>20500</v>
+        <v>20300</v>
       </c>
       <c r="J59" s="3">
+        <v>18900</v>
+      </c>
+      <c r="K59" s="3">
         <v>12400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,53 +3860,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>47200</v>
+        <v>30700</v>
       </c>
       <c r="E60" s="3">
-        <v>40800</v>
+        <v>43500</v>
       </c>
       <c r="F60" s="3">
-        <v>25300</v>
+        <v>37600</v>
       </c>
       <c r="G60" s="3">
-        <v>20000</v>
+        <v>23300</v>
       </c>
       <c r="H60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I60" s="3">
+        <v>28800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>26300</v>
+      </c>
+      <c r="K60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="L60" s="3">
+        <v>18000</v>
+      </c>
+      <c r="M60" s="3">
+        <v>33700</v>
+      </c>
+      <c r="N60" s="3">
         <v>31200</v>
       </c>
-      <c r="I60" s="3">
-        <v>28500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>18500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>18000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>33700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>31200</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17300</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,53 +3928,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>118000</v>
+        <v>110400</v>
       </c>
       <c r="E61" s="3">
-        <v>32500</v>
+        <v>108800</v>
       </c>
       <c r="F61" s="3">
-        <v>23000</v>
+        <v>29900</v>
       </c>
       <c r="G61" s="3">
-        <v>23900</v>
+        <v>39200</v>
       </c>
       <c r="H61" s="3">
-        <v>26500</v>
+        <v>40100</v>
       </c>
       <c r="I61" s="3">
-        <v>24700</v>
+        <v>41400</v>
       </c>
       <c r="J61" s="3">
+        <v>42200</v>
+      </c>
+      <c r="K61" s="3">
         <v>11200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3853,52 +3996,55 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19000</v>
+        <v>28800</v>
       </c>
       <c r="E62" s="3">
-        <v>8800</v>
+        <v>17500</v>
       </c>
       <c r="F62" s="3">
-        <v>24300</v>
+        <v>8100</v>
       </c>
       <c r="G62" s="3">
-        <v>22200</v>
+        <v>4400</v>
       </c>
       <c r="H62" s="3">
-        <v>20700</v>
+        <v>2400</v>
       </c>
       <c r="I62" s="3">
-        <v>22200</v>
+        <v>2100</v>
       </c>
       <c r="J62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2400</v>
       </c>
       <c r="P62" s="3">
         <v>2400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>2400</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3918,8 +4064,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3983,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4113,53 +4268,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>184500</v>
+        <v>170200</v>
       </c>
       <c r="E66" s="3">
-        <v>82600</v>
+        <v>170100</v>
       </c>
       <c r="F66" s="3">
-        <v>73200</v>
+        <v>76100</v>
       </c>
       <c r="G66" s="3">
-        <v>66700</v>
+        <v>67500</v>
       </c>
       <c r="H66" s="3">
-        <v>79000</v>
+        <v>61500</v>
       </c>
       <c r="I66" s="3">
-        <v>75800</v>
+        <v>72900</v>
       </c>
       <c r="J66" s="3">
+        <v>69800</v>
+      </c>
+      <c r="K66" s="3">
         <v>30600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>48900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4203,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4268,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4333,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4398,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4463,53 +4634,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>22300</v>
+        <v>19300</v>
       </c>
       <c r="E72" s="3">
-        <v>18400</v>
+        <v>20600</v>
       </c>
       <c r="F72" s="3">
-        <v>22700</v>
+        <v>17000</v>
       </c>
       <c r="G72" s="3">
-        <v>13000</v>
+        <v>20900</v>
       </c>
       <c r="H72" s="3">
-        <v>16300</v>
+        <v>12000</v>
       </c>
       <c r="I72" s="3">
-        <v>15900</v>
+        <v>15000</v>
       </c>
       <c r="J72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K72" s="3">
         <v>11700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20200</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
         <v>22100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4593,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4658,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4723,53 +4906,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>276400</v>
+        <v>249200</v>
       </c>
       <c r="E76" s="3">
-        <v>266600</v>
+        <v>254800</v>
       </c>
       <c r="F76" s="3">
-        <v>273300</v>
+        <v>245800</v>
       </c>
       <c r="G76" s="3">
-        <v>268400</v>
+        <v>252000</v>
       </c>
       <c r="H76" s="3">
-        <v>275100</v>
+        <v>247400</v>
       </c>
       <c r="I76" s="3">
-        <v>277100</v>
+        <v>253600</v>
       </c>
       <c r="J76" s="3">
+        <v>255400</v>
+      </c>
+      <c r="K76" s="3">
         <v>274400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>284000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>290900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>288500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>298300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4853,67 +5042,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4923,62 +5115,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12900</v>
+        <v>8500</v>
       </c>
       <c r="E81" s="3">
-        <v>6400</v>
+        <v>11800</v>
       </c>
       <c r="F81" s="3">
-        <v>18400</v>
+        <v>5900</v>
       </c>
       <c r="G81" s="3">
-        <v>6600</v>
+        <v>17000</v>
       </c>
       <c r="H81" s="3">
-        <v>11700</v>
+        <v>6000</v>
       </c>
       <c r="I81" s="3">
-        <v>13900</v>
+        <v>10800</v>
       </c>
       <c r="J81" s="3">
-        <v>9300</v>
+        <v>12800</v>
       </c>
       <c r="K81" s="3">
         <v>9300</v>
       </c>
       <c r="L81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M81" s="3">
         <v>11600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>22400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4988,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5013,8 +5211,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5022,16 +5221,16 @@
         <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
@@ -5043,32 +5242,32 @@
         <v>700</v>
       </c>
       <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5078,8 +5277,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5143,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5208,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5273,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5338,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5403,62 +5617,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14000</v>
+        <v>21900</v>
       </c>
       <c r="E89" s="3">
-        <v>14100</v>
+        <v>12900</v>
       </c>
       <c r="F89" s="3">
-        <v>17500</v>
+        <v>13000</v>
       </c>
       <c r="G89" s="3">
-        <v>-2700</v>
+        <v>16100</v>
       </c>
       <c r="H89" s="3">
-        <v>9000</v>
+        <v>-2500</v>
       </c>
       <c r="I89" s="3">
-        <v>15600</v>
+        <v>8300</v>
       </c>
       <c r="J89" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K89" s="3">
         <v>7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>5700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>32200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5493,62 +5713,63 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5558,8 +5779,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5623,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5688,62 +5915,65 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2100</v>
+        <v>-26100</v>
       </c>
       <c r="E94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G94" s="3">
+        <v>7600</v>
+      </c>
+      <c r="H94" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I94" s="3">
+        <v>12900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="K94" s="3">
         <v>9800</v>
       </c>
-      <c r="F94" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H94" s="3">
-        <v>14000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>9800</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>13700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5753,8 +5983,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5778,44 +6011,45 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="H96" s="3">
         <v>-9000</v>
       </c>
-      <c r="E96" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-11600</v>
-      </c>
       <c r="I96" s="3">
-        <v>-9900</v>
+        <v>-10700</v>
       </c>
       <c r="J96" s="3">
         <v>-9100</v>
       </c>
       <c r="K96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="L96" s="3">
         <v>-12100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-10500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-17900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5843,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5908,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5973,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6038,62 +6281,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>83700</v>
+        <v>-20000</v>
       </c>
       <c r="E100" s="3">
-        <v>-18200</v>
+        <v>77200</v>
       </c>
       <c r="F100" s="3">
-        <v>-14700</v>
+        <v>-16800</v>
       </c>
       <c r="G100" s="3">
-        <v>-15800</v>
+        <v>-13500</v>
       </c>
       <c r="H100" s="3">
-        <v>-15300</v>
+        <v>-14500</v>
       </c>
       <c r="I100" s="3">
-        <v>2700</v>
+        <v>-14100</v>
       </c>
       <c r="J100" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-13100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-22000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>-9700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-27800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>-3800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6103,62 +6349,65 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>400</v>
-      </c>
       <c r="F101" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="G101" s="3">
         <v>-400</v>
       </c>
       <c r="H101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>200</v>
+      </c>
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>500</v>
+      </c>
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>500</v>
-      </c>
-      <c r="M101" s="3">
-        <v>300</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
+        <v>600</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6168,62 +6417,65 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>95400</v>
+        <v>-23700</v>
       </c>
       <c r="E102" s="3">
-        <v>6100</v>
+        <v>88000</v>
       </c>
       <c r="F102" s="3">
-        <v>10600</v>
+        <v>5600</v>
       </c>
       <c r="G102" s="3">
-        <v>-7100</v>
+        <v>9800</v>
       </c>
       <c r="H102" s="3">
-        <v>7900</v>
+        <v>-6500</v>
       </c>
       <c r="I102" s="3">
-        <v>7900</v>
+        <v>7200</v>
       </c>
       <c r="J102" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K102" s="3">
         <v>3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6231,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,96 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,65 +756,68 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>20200</v>
+        <v>23600</v>
       </c>
       <c r="E8" s="3">
-        <v>23200</v>
+        <v>19600</v>
       </c>
       <c r="F8" s="3">
-        <v>20200</v>
+        <v>22500</v>
       </c>
       <c r="G8" s="3">
-        <v>21700</v>
+        <v>19600</v>
       </c>
       <c r="H8" s="3">
-        <v>18900</v>
+        <v>21100</v>
       </c>
       <c r="I8" s="3">
-        <v>20600</v>
+        <v>18400</v>
       </c>
       <c r="J8" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K8" s="3">
         <v>19000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,8 +827,11 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,8 +898,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +998,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,8 +1138,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1189,8 +1209,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1198,13 +1221,13 @@
         <v>1000</v>
       </c>
       <c r="E15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
       </c>
-      <c r="F15" s="3">
-        <v>1100</v>
-      </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="3">
         <v>800</v>
@@ -1213,7 +1236,7 @@
         <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
@@ -1222,32 +1245,32 @@
         <v>700</v>
       </c>
       <c r="M15" s="3">
+        <v>700</v>
+      </c>
+      <c r="N15" s="3">
         <v>800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>700</v>
       </c>
       <c r="O15" s="3">
         <v>700</v>
       </c>
       <c r="P15" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2400</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,65 +1306,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11400</v>
+        <v>15000</v>
       </c>
       <c r="E17" s="3">
-        <v>13200</v>
+        <v>11100</v>
       </c>
       <c r="F17" s="3">
-        <v>11400</v>
+        <v>12800</v>
       </c>
       <c r="G17" s="3">
-        <v>12000</v>
+        <v>11100</v>
       </c>
       <c r="H17" s="3">
-        <v>10000</v>
+        <v>11700</v>
       </c>
       <c r="I17" s="3">
-        <v>11400</v>
+        <v>9700</v>
       </c>
       <c r="J17" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K17" s="3">
         <v>11000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,65 +1375,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8800</v>
+        <v>8600</v>
       </c>
       <c r="E18" s="3">
-        <v>10000</v>
+        <v>8500</v>
       </c>
       <c r="F18" s="3">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="G18" s="3">
-        <v>9700</v>
+        <v>8500</v>
       </c>
       <c r="H18" s="3">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="I18" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L18" s="3">
         <v>9200</v>
       </c>
-      <c r="J18" s="3">
-        <v>7900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>9200</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>29500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,65 +1475,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>9800</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I20" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K20" s="3">
         <v>7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,65 +1544,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14600</v>
+        <v>11300</v>
       </c>
       <c r="E21" s="3">
-        <v>15800</v>
+        <v>14200</v>
       </c>
       <c r="F21" s="3">
-        <v>9300</v>
+        <v>15400</v>
       </c>
       <c r="G21" s="3">
-        <v>20400</v>
+        <v>9100</v>
       </c>
       <c r="H21" s="3">
-        <v>9800</v>
+        <v>19800</v>
       </c>
       <c r="I21" s="3">
-        <v>15400</v>
+        <v>9500</v>
       </c>
       <c r="J21" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K21" s="3">
         <v>16000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>13500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>32500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>15500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,40 +1615,43 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="E22" s="3">
-        <v>400</v>
+        <v>3100</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
       </c>
       <c r="G22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>500</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
       </c>
       <c r="K22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>500</v>
       </c>
       <c r="M22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
@@ -1623,20 +1663,20 @@
         <v>600</v>
       </c>
       <c r="Q22" s="3">
+        <v>600</v>
+      </c>
+      <c r="R22" s="3">
         <v>1800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>600</v>
       </c>
       <c r="S22" s="3">
         <v>600</v>
       </c>
       <c r="T22" s="3">
+        <v>600</v>
+      </c>
+      <c r="U22" s="3">
         <v>1700</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,65 +1686,68 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>10400</v>
+        <v>7200</v>
       </c>
       <c r="E23" s="3">
-        <v>14500</v>
+        <v>10100</v>
       </c>
       <c r="F23" s="3">
-        <v>7800</v>
+        <v>14100</v>
       </c>
       <c r="G23" s="3">
-        <v>19100</v>
+        <v>7600</v>
       </c>
       <c r="H23" s="3">
-        <v>8400</v>
+        <v>18600</v>
       </c>
       <c r="I23" s="3">
-        <v>14100</v>
+        <v>8200</v>
       </c>
       <c r="J23" s="3">
+        <v>13700</v>
+      </c>
+      <c r="K23" s="3">
         <v>14800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>28800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>23800</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,65 +1757,68 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
-        <v>2200</v>
-      </c>
       <c r="H24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>2200</v>
       </c>
       <c r="S24" s="3">
         <v>2200</v>
       </c>
       <c r="T24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U24" s="3">
         <v>5000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,65 +1899,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8400</v>
+        <v>5100</v>
       </c>
       <c r="E26" s="3">
-        <v>11700</v>
+        <v>8200</v>
       </c>
       <c r="F26" s="3">
+        <v>11400</v>
+      </c>
+      <c r="G26" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I26" s="3">
         <v>5900</v>
       </c>
-      <c r="G26" s="3">
-        <v>16900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>10800</v>
-      </c>
       <c r="J26" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K26" s="3">
         <v>12800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>9300</v>
       </c>
       <c r="L26" s="3">
         <v>9300</v>
       </c>
       <c r="M26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N26" s="3">
         <v>11600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>22900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>11800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,65 +1970,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="E27" s="3">
-        <v>11800</v>
+        <v>8300</v>
       </c>
       <c r="F27" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G27" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I27" s="3">
         <v>5900</v>
       </c>
-      <c r="G27" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>10800</v>
-      </c>
       <c r="J27" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K27" s="3">
         <v>12800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>9300</v>
       </c>
       <c r="L27" s="3">
         <v>9300</v>
       </c>
       <c r="M27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N27" s="3">
         <v>11600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>22400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,65 +2325,68 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-9800</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-9600</v>
       </c>
       <c r="I32" s="3">
-        <v>-5300</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,65 +2396,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="E33" s="3">
-        <v>11800</v>
+        <v>8300</v>
       </c>
       <c r="F33" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G33" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I33" s="3">
         <v>5900</v>
       </c>
-      <c r="G33" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>10800</v>
-      </c>
       <c r="J33" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K33" s="3">
         <v>12800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>9300</v>
       </c>
       <c r="L33" s="3">
         <v>9300</v>
       </c>
       <c r="M33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N33" s="3">
         <v>11600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>22400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,65 +2538,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="E35" s="3">
-        <v>11800</v>
+        <v>8300</v>
       </c>
       <c r="F35" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G35" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I35" s="3">
         <v>5900</v>
       </c>
-      <c r="G35" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>10800</v>
-      </c>
       <c r="J35" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K35" s="3">
         <v>12800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>9300</v>
       </c>
       <c r="L35" s="3">
         <v>9300</v>
       </c>
       <c r="M35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N35" s="3">
         <v>11600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>22400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,70 +2609,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,56 +2741,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8500</v>
+        <v>8200</v>
       </c>
       <c r="E41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
-        <v>7000</v>
-      </c>
       <c r="G41" s="3">
-        <v>5800</v>
+        <v>6800</v>
       </c>
       <c r="H41" s="3">
-        <v>4200</v>
+        <v>5600</v>
       </c>
       <c r="I41" s="3">
-        <v>5600</v>
+        <v>4100</v>
       </c>
       <c r="J41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K41" s="3">
         <v>2600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,8 +2810,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2791,56 +2881,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>17500</v>
+        <v>14100</v>
       </c>
       <c r="E43" s="3">
-        <v>19900</v>
+        <v>17100</v>
       </c>
       <c r="F43" s="3">
-        <v>13500</v>
+        <v>19400</v>
       </c>
       <c r="G43" s="3">
-        <v>13300</v>
+        <v>13100</v>
       </c>
       <c r="H43" s="3">
-        <v>11800</v>
+        <v>13000</v>
       </c>
       <c r="I43" s="3">
-        <v>11200</v>
+        <v>11400</v>
       </c>
       <c r="J43" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K43" s="3">
         <v>9700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>9800</v>
       </c>
       <c r="N43" s="3">
         <v>9800</v>
       </c>
       <c r="O43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P43" s="3">
         <v>12200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7300</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2952,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2927,56 +3023,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>320200</v>
+        <v>337600</v>
       </c>
       <c r="E45" s="3">
-        <v>338500</v>
+        <v>311500</v>
       </c>
       <c r="F45" s="3">
-        <v>239600</v>
+        <v>329200</v>
       </c>
       <c r="G45" s="3">
-        <v>243900</v>
+        <v>233100</v>
       </c>
       <c r="H45" s="3">
-        <v>235700</v>
+        <v>237200</v>
       </c>
       <c r="I45" s="3">
-        <v>252500</v>
+        <v>229300</v>
       </c>
       <c r="J45" s="3">
+        <v>245600</v>
+      </c>
+      <c r="K45" s="3">
         <v>258600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>270300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>279800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>299800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>292400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>291600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21300</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,56 +3094,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>346200</v>
+        <v>360000</v>
       </c>
       <c r="E46" s="3">
-        <v>361300</v>
+        <v>336800</v>
       </c>
       <c r="F46" s="3">
-        <v>260100</v>
+        <v>351500</v>
       </c>
       <c r="G46" s="3">
-        <v>263000</v>
+        <v>253000</v>
       </c>
       <c r="H46" s="3">
-        <v>251700</v>
+        <v>255800</v>
       </c>
       <c r="I46" s="3">
-        <v>269300</v>
+        <v>244900</v>
       </c>
       <c r="J46" s="3">
+        <v>262000</v>
+      </c>
+      <c r="K46" s="3">
         <v>270900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>282800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>291200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>314000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>307500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,56 +3165,59 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>14000</v>
+        <v>16300</v>
       </c>
       <c r="E47" s="3">
-        <v>4500</v>
+        <v>13600</v>
       </c>
       <c r="F47" s="3">
-        <v>7800</v>
+        <v>4300</v>
       </c>
       <c r="G47" s="3">
-        <v>4400</v>
+        <v>7600</v>
       </c>
       <c r="H47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K47" s="3">
         <v>5000</v>
       </c>
-      <c r="I47" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J47" s="3">
-        <v>5000</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,55 +3236,58 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12700</v>
+        <v>11800</v>
       </c>
       <c r="E48" s="3">
-        <v>13400</v>
+        <v>12400</v>
       </c>
       <c r="F48" s="3">
-        <v>13500</v>
+        <v>13000</v>
       </c>
       <c r="G48" s="3">
-        <v>14100</v>
+        <v>13200</v>
       </c>
       <c r="H48" s="3">
-        <v>14800</v>
+        <v>13700</v>
       </c>
       <c r="I48" s="3">
-        <v>15400</v>
+        <v>14400</v>
       </c>
       <c r="J48" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K48" s="3">
         <v>13300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>19700</v>
       </c>
       <c r="Q48" s="3">
         <v>19700</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>19700</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3199,37 +3307,40 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>39800</v>
+        <v>44900</v>
       </c>
       <c r="E49" s="3">
-        <v>39700</v>
+        <v>38700</v>
       </c>
       <c r="F49" s="3">
-        <v>38100</v>
+        <v>38600</v>
       </c>
       <c r="G49" s="3">
-        <v>35800</v>
+        <v>37000</v>
       </c>
       <c r="H49" s="3">
-        <v>35400</v>
+        <v>34900</v>
       </c>
       <c r="I49" s="3">
-        <v>35000</v>
+        <v>34500</v>
       </c>
       <c r="J49" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K49" s="3">
         <v>34500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>200</v>
       </c>
       <c r="M49" s="3">
         <v>200</v>
@@ -3241,13 +3352,13 @@
         <v>200</v>
       </c>
       <c r="P49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q49" s="3">
         <v>300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>300</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3267,8 +3378,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,31 +3520,34 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6600</v>
+        <v>8300</v>
       </c>
       <c r="E52" s="3">
-        <v>6100</v>
+        <v>6500</v>
       </c>
       <c r="F52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G52" s="3">
         <v>2300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2200</v>
       </c>
       <c r="H52" s="3">
         <v>2100</v>
       </c>
       <c r="I52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1600</v>
       </c>
       <c r="K52" s="3">
         <v>1600</v>
@@ -3436,23 +3556,23 @@
         <v>1600</v>
       </c>
       <c r="M52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N52" s="3">
         <v>1400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1100</v>
       </c>
       <c r="P52" s="3">
         <v>1100</v>
       </c>
       <c r="Q52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R52" s="3">
         <v>1300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,56 +3662,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>419300</v>
+        <v>441300</v>
       </c>
       <c r="E54" s="3">
-        <v>424900</v>
+        <v>407900</v>
       </c>
       <c r="F54" s="3">
-        <v>321900</v>
+        <v>413300</v>
       </c>
       <c r="G54" s="3">
-        <v>319400</v>
+        <v>313100</v>
       </c>
       <c r="H54" s="3">
-        <v>308900</v>
+        <v>310700</v>
       </c>
       <c r="I54" s="3">
-        <v>326500</v>
+        <v>300500</v>
       </c>
       <c r="J54" s="3">
+        <v>317600</v>
+      </c>
+      <c r="K54" s="3">
         <v>325300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>305000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>315300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>338700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>337400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>338400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>61500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,56 +3789,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1500</v>
       </c>
       <c r="L57" s="3">
         <v>1500</v>
       </c>
       <c r="M57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>23700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,56 +3858,59 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>19100</v>
+        <v>18200</v>
       </c>
       <c r="E58" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="F58" s="3">
-        <v>16700</v>
+        <v>18200</v>
       </c>
       <c r="G58" s="3">
-        <v>8600</v>
+        <v>16300</v>
       </c>
       <c r="H58" s="3">
-        <v>6400</v>
+        <v>8400</v>
       </c>
       <c r="I58" s="3">
-        <v>6900</v>
+        <v>6200</v>
       </c>
       <c r="J58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K58" s="3">
         <v>6000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>4700</v>
       </c>
       <c r="L58" s="3">
         <v>4700</v>
       </c>
       <c r="M58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N58" s="3">
         <v>4600</v>
-      </c>
-      <c r="N58" s="3">
-        <v>4100</v>
       </c>
       <c r="O58" s="3">
         <v>4100</v>
       </c>
       <c r="P58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Q58" s="3">
         <v>3700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,56 +3929,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11500</v>
+        <v>15200</v>
       </c>
       <c r="E59" s="3">
-        <v>23300</v>
+        <v>11200</v>
       </c>
       <c r="F59" s="3">
-        <v>19400</v>
+        <v>22700</v>
       </c>
       <c r="G59" s="3">
-        <v>13300</v>
+        <v>18900</v>
       </c>
       <c r="H59" s="3">
-        <v>10800</v>
+        <v>12900</v>
       </c>
       <c r="I59" s="3">
-        <v>20300</v>
+        <v>10500</v>
       </c>
       <c r="J59" s="3">
+        <v>19800</v>
+      </c>
+      <c r="K59" s="3">
         <v>18900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,56 +4000,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>30700</v>
+        <v>33700</v>
       </c>
       <c r="E60" s="3">
-        <v>43500</v>
+        <v>29800</v>
       </c>
       <c r="F60" s="3">
-        <v>37600</v>
+        <v>42300</v>
       </c>
       <c r="G60" s="3">
-        <v>23300</v>
+        <v>36600</v>
       </c>
       <c r="H60" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I60" s="3">
+        <v>18000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K60" s="3">
+        <v>26300</v>
+      </c>
+      <c r="L60" s="3">
         <v>18500</v>
       </c>
-      <c r="I60" s="3">
-        <v>28800</v>
-      </c>
-      <c r="J60" s="3">
-        <v>26300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>18500</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17300</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,56 +4071,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>110400</v>
+        <v>124200</v>
       </c>
       <c r="E61" s="3">
-        <v>108800</v>
+        <v>107400</v>
       </c>
       <c r="F61" s="3">
-        <v>29900</v>
+        <v>105800</v>
       </c>
       <c r="G61" s="3">
-        <v>39200</v>
+        <v>29100</v>
       </c>
       <c r="H61" s="3">
-        <v>40100</v>
+        <v>38200</v>
       </c>
       <c r="I61" s="3">
-        <v>41400</v>
+        <v>39000</v>
       </c>
       <c r="J61" s="3">
+        <v>40300</v>
+      </c>
+      <c r="K61" s="3">
         <v>42200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3999,55 +4142,58 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28800</v>
+        <v>43200</v>
       </c>
       <c r="E62" s="3">
-        <v>17500</v>
+        <v>28000</v>
       </c>
       <c r="F62" s="3">
-        <v>8100</v>
+        <v>17000</v>
       </c>
       <c r="G62" s="3">
-        <v>4400</v>
+        <v>7900</v>
       </c>
       <c r="H62" s="3">
-        <v>2400</v>
+        <v>4300</v>
       </c>
       <c r="I62" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="J62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1900</v>
-      </c>
-      <c r="P62" s="3">
-        <v>2400</v>
       </c>
       <c r="Q62" s="3">
         <v>2400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>2400</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -4067,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,56 +4426,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>170200</v>
+        <v>201300</v>
       </c>
       <c r="E66" s="3">
-        <v>170100</v>
+        <v>165500</v>
       </c>
       <c r="F66" s="3">
-        <v>76100</v>
+        <v>165500</v>
       </c>
       <c r="G66" s="3">
-        <v>67500</v>
+        <v>74100</v>
       </c>
       <c r="H66" s="3">
-        <v>61500</v>
+        <v>65600</v>
       </c>
       <c r="I66" s="3">
-        <v>72900</v>
+        <v>59800</v>
       </c>
       <c r="J66" s="3">
+        <v>70900</v>
+      </c>
+      <c r="K66" s="3">
         <v>69800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>40000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>57900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,56 +4808,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>19300</v>
+        <v>15700</v>
       </c>
       <c r="E72" s="3">
-        <v>20600</v>
+        <v>18700</v>
       </c>
       <c r="F72" s="3">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="G72" s="3">
-        <v>20900</v>
+        <v>16500</v>
       </c>
       <c r="H72" s="3">
-        <v>12000</v>
+        <v>20300</v>
       </c>
       <c r="I72" s="3">
-        <v>15000</v>
+        <v>11700</v>
       </c>
       <c r="J72" s="3">
         <v>14600</v>
       </c>
       <c r="K72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="L72" s="3">
         <v>11700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20200</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
       <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
         <v>22100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,56 +5092,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>249200</v>
+        <v>240000</v>
       </c>
       <c r="E76" s="3">
-        <v>254800</v>
+        <v>242400</v>
       </c>
       <c r="F76" s="3">
-        <v>245800</v>
+        <v>247800</v>
       </c>
       <c r="G76" s="3">
-        <v>252000</v>
+        <v>239100</v>
       </c>
       <c r="H76" s="3">
-        <v>247400</v>
+        <v>245100</v>
       </c>
       <c r="I76" s="3">
-        <v>253600</v>
+        <v>240700</v>
       </c>
       <c r="J76" s="3">
+        <v>246700</v>
+      </c>
+      <c r="K76" s="3">
         <v>255400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>274400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>284000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>290900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>288500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>298300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,70 +5234,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,65 +5310,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8500</v>
+        <v>5200</v>
       </c>
       <c r="E81" s="3">
-        <v>11800</v>
+        <v>8300</v>
       </c>
       <c r="F81" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G81" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I81" s="3">
         <v>5900</v>
       </c>
-      <c r="G81" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>10800</v>
-      </c>
       <c r="J81" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K81" s="3">
         <v>12800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>9300</v>
       </c>
       <c r="L81" s="3">
         <v>9300</v>
       </c>
       <c r="M81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N81" s="3">
         <v>11600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>22400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,8 +5410,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5221,13 +5420,13 @@
         <v>1000</v>
       </c>
       <c r="E83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F83" s="3">
         <v>900</v>
       </c>
-      <c r="F83" s="3">
-        <v>1100</v>
-      </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>800</v>
@@ -5236,7 +5435,7 @@
         <v>800</v>
       </c>
       <c r="J83" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
@@ -5245,32 +5444,32 @@
         <v>700</v>
       </c>
       <c r="M83" s="3">
+        <v>700</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1900</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2400</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5280,8 +5479,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,65 +5834,68 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>21900</v>
+        <v>28200</v>
       </c>
       <c r="E89" s="3">
-        <v>12900</v>
+        <v>21300</v>
       </c>
       <c r="F89" s="3">
-        <v>13000</v>
+        <v>12600</v>
       </c>
       <c r="G89" s="3">
-        <v>16100</v>
+        <v>12700</v>
       </c>
       <c r="H89" s="3">
-        <v>-2500</v>
+        <v>15700</v>
       </c>
       <c r="I89" s="3">
-        <v>8300</v>
+        <v>-2400</v>
       </c>
       <c r="J89" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K89" s="3">
         <v>14400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>23900</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>5700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,65 +5934,66 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,65 +6145,68 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-26100</v>
+        <v>-6200</v>
       </c>
       <c r="E94" s="3">
-        <v>-2000</v>
+        <v>-25300</v>
       </c>
       <c r="F94" s="3">
-        <v>9000</v>
+        <v>-1900</v>
       </c>
       <c r="G94" s="3">
-        <v>7600</v>
+        <v>8800</v>
       </c>
       <c r="H94" s="3">
-        <v>10900</v>
+        <v>7400</v>
       </c>
       <c r="I94" s="3">
-        <v>12900</v>
+        <v>10600</v>
       </c>
       <c r="J94" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>13700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>12700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6900</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5986,8 +6216,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,47 +6245,48 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-9800</v>
+        <v>-8600</v>
       </c>
       <c r="E96" s="3">
-        <v>-8300</v>
+        <v>-9600</v>
       </c>
       <c r="F96" s="3">
-        <v>-9900</v>
+        <v>-8100</v>
       </c>
       <c r="G96" s="3">
-        <v>-7900</v>
+        <v>-9700</v>
       </c>
       <c r="H96" s="3">
-        <v>-9000</v>
+        <v>-7700</v>
       </c>
       <c r="I96" s="3">
-        <v>-10700</v>
+        <v>-8700</v>
       </c>
       <c r="J96" s="3">
-        <v>-9100</v>
+        <v>-10400</v>
       </c>
       <c r="K96" s="3">
         <v>-9100</v>
       </c>
       <c r="L96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="M96" s="3">
         <v>-12100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-10500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-17900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,65 +6527,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-20000</v>
+        <v>-12100</v>
       </c>
       <c r="E100" s="3">
-        <v>77200</v>
+        <v>-19400</v>
       </c>
       <c r="F100" s="3">
-        <v>-16800</v>
+        <v>75100</v>
       </c>
       <c r="G100" s="3">
-        <v>-13500</v>
+        <v>-16300</v>
       </c>
       <c r="H100" s="3">
-        <v>-14500</v>
+        <v>-13200</v>
       </c>
       <c r="I100" s="3">
         <v>-14100</v>
       </c>
       <c r="J100" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-22000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-27800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>-3800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,65 +6598,68 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-400</v>
       </c>
       <c r="H101" s="3">
         <v>-400</v>
       </c>
       <c r="I101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6420,65 +6669,68 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-23700</v>
+        <v>10800</v>
       </c>
       <c r="E102" s="3">
-        <v>88000</v>
+        <v>-23100</v>
       </c>
       <c r="F102" s="3">
-        <v>5600</v>
+        <v>85600</v>
       </c>
       <c r="G102" s="3">
-        <v>9800</v>
+        <v>5400</v>
       </c>
       <c r="H102" s="3">
-        <v>-6500</v>
+        <v>9500</v>
       </c>
       <c r="I102" s="3">
-        <v>7200</v>
+        <v>-6400</v>
       </c>
       <c r="J102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K102" s="3">
         <v>7300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17800</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,100 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,68 +760,71 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E8" s="3">
         <v>23600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>21700</v>
+      </c>
+      <c r="G8" s="3">
+        <v>25900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>21800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>24400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>20200</v>
+      </c>
+      <c r="K8" s="3">
+        <v>20100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>19000</v>
+      </c>
+      <c r="M8" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N8" s="3">
+        <v>19300</v>
+      </c>
+      <c r="O8" s="3">
+        <v>23700</v>
+      </c>
+      <c r="P8" s="3">
+        <v>24900</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>24100</v>
+      </c>
+      <c r="R8" s="3">
         <v>19600</v>
       </c>
-      <c r="F8" s="3">
-        <v>22500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>19600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>18400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>20100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>19000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>20000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>19300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>23700</v>
-      </c>
-      <c r="O8" s="3">
-        <v>24900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>24100</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>19600</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,8 +834,11 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -901,31 +908,34 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>23600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>21700</v>
+      </c>
+      <c r="G10" s="3">
+        <v>25900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>21800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>24400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>20200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1012,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1010,11 +1024,11 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+      <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,31 +1158,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-3100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-6800</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-11900</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1212,34 +1232,37 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
         <v>1000</v>
       </c>
       <c r="F15" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
         <v>1000</v>
       </c>
       <c r="H15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>900</v>
+      </c>
+      <c r="J15" s="3">
+        <v>900</v>
+      </c>
+      <c r="K15" s="3">
         <v>800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
@@ -1248,32 +1271,32 @@
         <v>700</v>
       </c>
       <c r="N15" s="3">
+        <v>700</v>
+      </c>
+      <c r="O15" s="3">
         <v>800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>700</v>
       </c>
       <c r="P15" s="3">
         <v>700</v>
       </c>
       <c r="Q15" s="3">
+        <v>700</v>
+      </c>
+      <c r="R15" s="3">
         <v>600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2400</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,68 +1333,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E17" s="3">
         <v>15000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>12300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>14700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>13500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K17" s="3">
         <v>11100</v>
       </c>
-      <c r="F17" s="3">
-        <v>12800</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="L17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>10800</v>
+      </c>
+      <c r="N17" s="3">
         <v>11100</v>
       </c>
-      <c r="H17" s="3">
-        <v>11700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>9700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>11100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>10800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>11100</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15600</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,8 +1405,11 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1387,59 +1417,59 @@
         <v>8600</v>
       </c>
       <c r="E18" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="F18" s="3">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="G18" s="3">
-        <v>8500</v>
+        <v>11100</v>
       </c>
       <c r="H18" s="3">
         <v>9500</v>
       </c>
       <c r="I18" s="3">
-        <v>8700</v>
+        <v>10900</v>
       </c>
       <c r="J18" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K18" s="3">
         <v>9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>29500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22400</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,68 +1509,69 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1800</v>
+        <v>-1600</v>
       </c>
       <c r="E20" s="3">
-        <v>4700</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>4800</v>
+        <v>-1200</v>
       </c>
       <c r="G20" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="H20" s="3">
-        <v>9600</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2900</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,68 +1581,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="E21" s="3">
-        <v>14200</v>
+        <v>9600</v>
       </c>
       <c r="F21" s="3">
-        <v>15400</v>
+        <v>11700</v>
       </c>
       <c r="G21" s="3">
-        <v>9100</v>
+        <v>13300</v>
       </c>
       <c r="H21" s="3">
-        <v>19800</v>
+        <v>10800</v>
       </c>
       <c r="I21" s="3">
-        <v>9500</v>
+        <v>11800</v>
       </c>
       <c r="J21" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K21" s="3">
         <v>14900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>13500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>32500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>15500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,43 +1655,46 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="E22" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="F22" s="3">
-        <v>400</v>
+        <v>3500</v>
       </c>
       <c r="G22" s="3">
-        <v>400</v>
+        <v>2900</v>
       </c>
       <c r="H22" s="3">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="I22" s="3">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="J22" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
       </c>
       <c r="L22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>500</v>
       </c>
       <c r="N22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="O22" s="3">
         <v>600</v>
@@ -1666,20 +1706,20 @@
         <v>600</v>
       </c>
       <c r="R22" s="3">
+        <v>600</v>
+      </c>
+      <c r="S22" s="3">
         <v>1800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>600</v>
       </c>
       <c r="T22" s="3">
         <v>600</v>
       </c>
       <c r="U22" s="3">
+        <v>600</v>
+      </c>
+      <c r="V22" s="3">
         <v>1700</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1689,68 +1729,71 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E23" s="3">
         <v>7200</v>
       </c>
-      <c r="E23" s="3">
-        <v>10100</v>
-      </c>
       <c r="F23" s="3">
-        <v>14100</v>
+        <v>11200</v>
       </c>
       <c r="G23" s="3">
-        <v>7600</v>
+        <v>16100</v>
       </c>
       <c r="H23" s="3">
-        <v>18600</v>
+        <v>8400</v>
       </c>
       <c r="I23" s="3">
-        <v>8200</v>
+        <v>21400</v>
       </c>
       <c r="J23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K23" s="3">
         <v>13700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>28800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>23800</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,68 +1803,71 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
-        <v>1900</v>
-      </c>
       <c r="F24" s="3">
-        <v>2700</v>
+        <v>2100</v>
       </c>
       <c r="G24" s="3">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="H24" s="3">
         <v>2100</v>
       </c>
       <c r="I24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5900</v>
-      </c>
-      <c r="S24" s="3">
-        <v>2200</v>
       </c>
       <c r="T24" s="3">
         <v>2200</v>
       </c>
       <c r="U24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,68 +1951,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E26" s="3">
         <v>5100</v>
       </c>
-      <c r="E26" s="3">
-        <v>8200</v>
-      </c>
       <c r="F26" s="3">
-        <v>11400</v>
+        <v>9100</v>
       </c>
       <c r="G26" s="3">
-        <v>5700</v>
+        <v>13100</v>
       </c>
       <c r="H26" s="3">
-        <v>16500</v>
+        <v>6400</v>
       </c>
       <c r="I26" s="3">
-        <v>5900</v>
+        <v>19000</v>
       </c>
       <c r="J26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K26" s="3">
         <v>10500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>9300</v>
       </c>
       <c r="M26" s="3">
         <v>9300</v>
       </c>
       <c r="N26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O26" s="3">
         <v>11600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>22900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>11800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,68 +2025,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
-        <v>8300</v>
-      </c>
       <c r="F27" s="3">
-        <v>11500</v>
+        <v>9200</v>
       </c>
       <c r="G27" s="3">
-        <v>5800</v>
+        <v>13200</v>
       </c>
       <c r="H27" s="3">
-        <v>16500</v>
+        <v>6400</v>
       </c>
       <c r="I27" s="3">
-        <v>5900</v>
+        <v>19000</v>
       </c>
       <c r="J27" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K27" s="3">
         <v>10500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>9300</v>
       </c>
       <c r="M27" s="3">
         <v>9300</v>
       </c>
       <c r="N27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O27" s="3">
         <v>11600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>22400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,68 +2395,71 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1800</v>
+        <v>1600</v>
       </c>
       <c r="E32" s="3">
-        <v>-4700</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-4800</v>
+        <v>1200</v>
       </c>
       <c r="G32" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="H32" s="3">
-        <v>-9600</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2900</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,68 +2469,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
-        <v>8300</v>
-      </c>
       <c r="F33" s="3">
-        <v>11500</v>
+        <v>9200</v>
       </c>
       <c r="G33" s="3">
-        <v>5800</v>
+        <v>13200</v>
       </c>
       <c r="H33" s="3">
-        <v>16500</v>
+        <v>6400</v>
       </c>
       <c r="I33" s="3">
-        <v>5900</v>
+        <v>19000</v>
       </c>
       <c r="J33" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K33" s="3">
         <v>10500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>9300</v>
       </c>
       <c r="M33" s="3">
         <v>9300</v>
       </c>
       <c r="N33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O33" s="3">
         <v>11600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>22400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,68 +2617,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
-        <v>8300</v>
-      </c>
       <c r="F35" s="3">
-        <v>11500</v>
+        <v>9200</v>
       </c>
       <c r="G35" s="3">
-        <v>5800</v>
+        <v>13200</v>
       </c>
       <c r="H35" s="3">
-        <v>16500</v>
+        <v>6400</v>
       </c>
       <c r="I35" s="3">
-        <v>5900</v>
+        <v>19000</v>
       </c>
       <c r="J35" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K35" s="3">
         <v>10500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>9300</v>
       </c>
       <c r="M35" s="3">
         <v>9300</v>
       </c>
       <c r="N35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O35" s="3">
         <v>11600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>22400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,73 +2691,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,59 +2828,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8200</v>
+        <v>98100</v>
       </c>
       <c r="E41" s="3">
-        <v>8200</v>
+        <v>106700</v>
       </c>
       <c r="F41" s="3">
-        <v>2900</v>
+        <v>106100</v>
       </c>
       <c r="G41" s="3">
-        <v>6800</v>
+        <v>136100</v>
       </c>
       <c r="H41" s="3">
-        <v>5600</v>
+        <v>36900</v>
       </c>
       <c r="I41" s="3">
-        <v>4100</v>
+        <v>31900</v>
       </c>
       <c r="J41" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K41" s="3">
         <v>5400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,31 +2900,34 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>251100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>235600</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>243600</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>240800</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>226500</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>245300</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>232500</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2884,59 +2974,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14100</v>
+        <v>14900</v>
       </c>
       <c r="E43" s="3">
-        <v>17100</v>
+        <v>14200</v>
       </c>
       <c r="F43" s="3">
-        <v>19400</v>
+        <v>18900</v>
       </c>
       <c r="G43" s="3">
-        <v>13100</v>
+        <v>22200</v>
       </c>
       <c r="H43" s="3">
-        <v>13000</v>
+        <v>14600</v>
       </c>
       <c r="I43" s="3">
-        <v>11400</v>
+        <v>15000</v>
       </c>
       <c r="J43" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K43" s="3">
         <v>10900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>9800</v>
       </c>
       <c r="O43" s="3">
         <v>9800</v>
       </c>
       <c r="P43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Q43" s="3">
         <v>12200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7300</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,31 +3048,34 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3026,59 +3122,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>337600</v>
+        <v>4900</v>
       </c>
       <c r="E45" s="3">
-        <v>311500</v>
+        <v>4400</v>
       </c>
       <c r="F45" s="3">
-        <v>329200</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3">
-        <v>233100</v>
+        <v>3900</v>
       </c>
       <c r="H45" s="3">
-        <v>237200</v>
+        <v>3800</v>
       </c>
       <c r="I45" s="3">
-        <v>229300</v>
+        <v>3000</v>
       </c>
       <c r="J45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K45" s="3">
         <v>245600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>258600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>270300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>279800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>299800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>292400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>291600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,59 +3196,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>360000</v>
+        <v>369000</v>
       </c>
       <c r="E46" s="3">
-        <v>336800</v>
+        <v>360800</v>
       </c>
       <c r="F46" s="3">
-        <v>351500</v>
+        <v>373600</v>
       </c>
       <c r="G46" s="3">
-        <v>253000</v>
+        <v>403000</v>
       </c>
       <c r="H46" s="3">
-        <v>255800</v>
+        <v>281900</v>
       </c>
       <c r="I46" s="3">
-        <v>244900</v>
+        <v>295200</v>
       </c>
       <c r="J46" s="3">
+        <v>269100</v>
+      </c>
+      <c r="K46" s="3">
         <v>262000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>270900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>282800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>314000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>307500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>308500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,59 +3270,62 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>16300</v>
+        <v>13600</v>
       </c>
       <c r="E47" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="F47" s="3">
-        <v>4300</v>
+        <v>11600</v>
       </c>
       <c r="G47" s="3">
-        <v>7600</v>
+        <v>1500</v>
       </c>
       <c r="H47" s="3">
-        <v>4200</v>
+        <v>1400</v>
       </c>
       <c r="I47" s="3">
-        <v>4800</v>
+        <v>1300</v>
       </c>
       <c r="J47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K47" s="3">
         <v>4700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3239,58 +3344,61 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11800</v>
+        <v>11400</v>
       </c>
       <c r="E48" s="3">
-        <v>12400</v>
+        <v>11700</v>
       </c>
       <c r="F48" s="3">
-        <v>13000</v>
+        <v>13500</v>
       </c>
       <c r="G48" s="3">
-        <v>13200</v>
+        <v>14600</v>
       </c>
       <c r="H48" s="3">
-        <v>13700</v>
+        <v>14200</v>
       </c>
       <c r="I48" s="3">
-        <v>14400</v>
+        <v>15100</v>
       </c>
       <c r="J48" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K48" s="3">
         <v>15000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>19700</v>
       </c>
       <c r="R48" s="3">
         <v>19700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>19700</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3310,40 +3418,43 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>44900</v>
+        <v>42900</v>
       </c>
       <c r="E49" s="3">
-        <v>38700</v>
+        <v>41800</v>
       </c>
       <c r="F49" s="3">
-        <v>38600</v>
+        <v>39300</v>
       </c>
       <c r="G49" s="3">
-        <v>37000</v>
+        <v>40400</v>
       </c>
       <c r="H49" s="3">
-        <v>34900</v>
+        <v>39000</v>
       </c>
       <c r="I49" s="3">
+        <v>40000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>37600</v>
+      </c>
+      <c r="K49" s="3">
+        <v>34000</v>
+      </c>
+      <c r="L49" s="3">
         <v>34500</v>
       </c>
-      <c r="J49" s="3">
-        <v>34000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>34500</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>200</v>
       </c>
       <c r="N49" s="3">
         <v>200</v>
@@ -3355,13 +3466,13 @@
         <v>200</v>
       </c>
       <c r="Q49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R49" s="3">
         <v>300</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>300</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,34 +3640,37 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8300</v>
+        <v>5200</v>
       </c>
       <c r="E52" s="3">
-        <v>6500</v>
+        <v>5300</v>
       </c>
       <c r="F52" s="3">
-        <v>5900</v>
+        <v>4100</v>
       </c>
       <c r="G52" s="3">
-        <v>2300</v>
+        <v>4100</v>
       </c>
       <c r="H52" s="3">
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>1600</v>
@@ -3559,23 +3679,23 @@
         <v>1600</v>
       </c>
       <c r="N52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O52" s="3">
         <v>1400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1100</v>
       </c>
       <c r="Q52" s="3">
         <v>1100</v>
       </c>
       <c r="R52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,59 +3788,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>441300</v>
+        <v>451300</v>
       </c>
       <c r="E54" s="3">
-        <v>407900</v>
+        <v>442300</v>
       </c>
       <c r="F54" s="3">
-        <v>413300</v>
+        <v>452500</v>
       </c>
       <c r="G54" s="3">
-        <v>313100</v>
+        <v>473900</v>
       </c>
       <c r="H54" s="3">
-        <v>310700</v>
+        <v>348900</v>
       </c>
       <c r="I54" s="3">
-        <v>300500</v>
+        <v>358600</v>
       </c>
       <c r="J54" s="3">
+        <v>330200</v>
+      </c>
+      <c r="K54" s="3">
         <v>317600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>325300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>305000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>315300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>338700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>337400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>338400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>61500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>62500</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,59 +3920,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L57" s="3">
         <v>1400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1500</v>
       </c>
       <c r="M57" s="3">
         <v>1500</v>
       </c>
       <c r="N57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>23700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,59 +3992,62 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E58" s="3">
         <v>18200</v>
       </c>
-      <c r="E58" s="3">
-        <v>18600</v>
-      </c>
       <c r="F58" s="3">
-        <v>18200</v>
+        <v>20600</v>
       </c>
       <c r="G58" s="3">
-        <v>16300</v>
+        <v>20800</v>
       </c>
       <c r="H58" s="3">
-        <v>8400</v>
+        <v>18100</v>
       </c>
       <c r="I58" s="3">
-        <v>6200</v>
+        <v>9700</v>
       </c>
       <c r="J58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K58" s="3">
         <v>6700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>4700</v>
       </c>
       <c r="M58" s="3">
         <v>4700</v>
       </c>
       <c r="N58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O58" s="3">
         <v>4600</v>
-      </c>
-      <c r="O58" s="3">
-        <v>4100</v>
       </c>
       <c r="P58" s="3">
         <v>4100</v>
       </c>
       <c r="Q58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R58" s="3">
         <v>3700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,59 +4066,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15200</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="3">
-        <v>11200</v>
+        <v>3100</v>
       </c>
       <c r="F59" s="3">
-        <v>22700</v>
+        <v>5100</v>
       </c>
       <c r="G59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>19800</v>
+      </c>
+      <c r="L59" s="3">
         <v>18900</v>
       </c>
-      <c r="H59" s="3">
-        <v>12900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>10500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>19800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>18900</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,59 +4140,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>33800</v>
+      </c>
+      <c r="F60" s="3">
+        <v>33100</v>
+      </c>
+      <c r="G60" s="3">
+        <v>48500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>40800</v>
+      </c>
+      <c r="I60" s="3">
+        <v>26200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>19700</v>
+      </c>
+      <c r="K60" s="3">
+        <v>28000</v>
+      </c>
+      <c r="L60" s="3">
+        <v>26300</v>
+      </c>
+      <c r="M60" s="3">
+        <v>18500</v>
+      </c>
+      <c r="N60" s="3">
+        <v>18000</v>
+      </c>
+      <c r="O60" s="3">
         <v>33700</v>
       </c>
-      <c r="E60" s="3">
-        <v>29800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>42300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>36600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>22700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>28000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>26300</v>
-      </c>
-      <c r="L60" s="3">
-        <v>18500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>18000</v>
-      </c>
-      <c r="N60" s="3">
-        <v>33700</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17300</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,59 +4214,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>124200</v>
+        <v>123200</v>
       </c>
       <c r="E61" s="3">
-        <v>107400</v>
+        <v>124500</v>
       </c>
       <c r="F61" s="3">
-        <v>105800</v>
+        <v>119200</v>
       </c>
       <c r="G61" s="3">
-        <v>29100</v>
+        <v>121300</v>
       </c>
       <c r="H61" s="3">
-        <v>38200</v>
+        <v>32400</v>
       </c>
       <c r="I61" s="3">
-        <v>39000</v>
+        <v>44000</v>
       </c>
       <c r="J61" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K61" s="3">
         <v>40300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4145,58 +4288,61 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>43200</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>28000</v>
+        <v>1200</v>
       </c>
       <c r="F62" s="3">
-        <v>17000</v>
+        <v>1400</v>
       </c>
       <c r="G62" s="3">
-        <v>7900</v>
+        <v>1100</v>
       </c>
       <c r="H62" s="3">
-        <v>4300</v>
+        <v>900</v>
       </c>
       <c r="I62" s="3">
-        <v>2300</v>
+        <v>600</v>
       </c>
       <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2400</v>
       </c>
       <c r="R62" s="3">
         <v>2400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>2400</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,59 +4584,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>201300</v>
+        <v>211000</v>
       </c>
       <c r="E66" s="3">
-        <v>165500</v>
+        <v>201600</v>
       </c>
       <c r="F66" s="3">
-        <v>165500</v>
+        <v>183300</v>
       </c>
       <c r="G66" s="3">
-        <v>74100</v>
+        <v>189400</v>
       </c>
       <c r="H66" s="3">
-        <v>65600</v>
+        <v>82000</v>
       </c>
       <c r="I66" s="3">
-        <v>59800</v>
+        <v>75200</v>
       </c>
       <c r="J66" s="3">
+        <v>65100</v>
+      </c>
+      <c r="K66" s="3">
         <v>70900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>69800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>40000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,59 +4982,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E72" s="3">
         <v>15700</v>
       </c>
-      <c r="E72" s="3">
-        <v>18700</v>
-      </c>
       <c r="F72" s="3">
-        <v>20000</v>
+        <v>20800</v>
       </c>
       <c r="G72" s="3">
-        <v>16500</v>
+        <v>23000</v>
       </c>
       <c r="H72" s="3">
-        <v>20300</v>
+        <v>18400</v>
       </c>
       <c r="I72" s="3">
-        <v>11700</v>
+        <v>23500</v>
       </c>
       <c r="J72" s="3">
-        <v>14600</v>
+        <v>12800</v>
       </c>
       <c r="K72" s="3">
         <v>14600</v>
       </c>
       <c r="L72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="M72" s="3">
         <v>11700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20200</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3">
         <v>22100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,59 +5278,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>240000</v>
+        <v>240200</v>
       </c>
       <c r="E76" s="3">
-        <v>242400</v>
+        <v>240600</v>
       </c>
       <c r="F76" s="3">
-        <v>247800</v>
+        <v>268900</v>
       </c>
       <c r="G76" s="3">
-        <v>239100</v>
+        <v>284200</v>
       </c>
       <c r="H76" s="3">
-        <v>245100</v>
+        <v>266400</v>
       </c>
       <c r="I76" s="3">
-        <v>240700</v>
+        <v>282800</v>
       </c>
       <c r="J76" s="3">
+        <v>264500</v>
+      </c>
+      <c r="K76" s="3">
         <v>246700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>255400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>274400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>284000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>290900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>288500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>298300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,73 +5426,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,68 +5505,71 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
-        <v>8300</v>
-      </c>
       <c r="F81" s="3">
-        <v>11500</v>
+        <v>9200</v>
       </c>
       <c r="G81" s="3">
-        <v>5800</v>
+        <v>13200</v>
       </c>
       <c r="H81" s="3">
-        <v>16500</v>
+        <v>6400</v>
       </c>
       <c r="I81" s="3">
-        <v>5900</v>
+        <v>19000</v>
       </c>
       <c r="J81" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K81" s="3">
         <v>10500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>9300</v>
       </c>
       <c r="M81" s="3">
         <v>9300</v>
       </c>
       <c r="N81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O81" s="3">
         <v>11600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>22400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,34 +5609,35 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
@@ -5447,32 +5646,32 @@
         <v>700</v>
       </c>
       <c r="N83" s="3">
+        <v>700</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1900</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2400</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,68 +6051,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>28200</v>
+        <v>-12700</v>
       </c>
       <c r="E89" s="3">
-        <v>21300</v>
+        <v>28300</v>
       </c>
       <c r="F89" s="3">
-        <v>12600</v>
+        <v>23600</v>
       </c>
       <c r="G89" s="3">
-        <v>12700</v>
+        <v>14400</v>
       </c>
       <c r="H89" s="3">
-        <v>15700</v>
+        <v>14100</v>
       </c>
       <c r="I89" s="3">
-        <v>-2400</v>
+        <v>18100</v>
       </c>
       <c r="J89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K89" s="3">
         <v>8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>5700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>4600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,68 +6155,69 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4100</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
-        <v>-3300</v>
+        <v>-700</v>
       </c>
       <c r="F91" s="3">
-        <v>-11000</v>
+        <v>-700</v>
       </c>
       <c r="G91" s="3">
-        <v>-15900</v>
+        <v>-2300</v>
       </c>
       <c r="H91" s="3">
-        <v>-5600</v>
+        <v>-3200</v>
       </c>
       <c r="I91" s="3">
-        <v>-4200</v>
+        <v>-1200</v>
       </c>
       <c r="J91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,68 +6375,71 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
-        <v>-25300</v>
-      </c>
       <c r="F94" s="3">
-        <v>-1900</v>
+        <v>-28100</v>
       </c>
       <c r="G94" s="3">
-        <v>8800</v>
+        <v>-2200</v>
       </c>
       <c r="H94" s="3">
-        <v>7400</v>
+        <v>9800</v>
       </c>
       <c r="I94" s="3">
-        <v>10600</v>
+        <v>8500</v>
       </c>
       <c r="J94" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K94" s="3">
         <v>12500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>13700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>2000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>12700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6900</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,50 +6479,51 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8600</v>
+        <v>9400</v>
       </c>
       <c r="E96" s="3">
-        <v>-9600</v>
+        <v>8600</v>
       </c>
       <c r="F96" s="3">
-        <v>-8100</v>
+        <v>10600</v>
       </c>
       <c r="G96" s="3">
-        <v>-9700</v>
+        <v>9200</v>
       </c>
       <c r="H96" s="3">
-        <v>-7700</v>
+        <v>10800</v>
       </c>
       <c r="I96" s="3">
-        <v>-8700</v>
+        <v>8900</v>
       </c>
       <c r="J96" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-10400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-9100</v>
       </c>
       <c r="L96" s="3">
         <v>-9100</v>
       </c>
       <c r="M96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="N96" s="3">
         <v>-12100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-10500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-17900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,68 +6773,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12100</v>
       </c>
-      <c r="E100" s="3">
-        <v>-19400</v>
-      </c>
       <c r="F100" s="3">
-        <v>75100</v>
+        <v>-21500</v>
       </c>
       <c r="G100" s="3">
-        <v>-16300</v>
+        <v>86100</v>
       </c>
       <c r="H100" s="3">
-        <v>-13200</v>
+        <v>-18200</v>
       </c>
       <c r="I100" s="3">
-        <v>-14100</v>
+        <v>-15200</v>
       </c>
       <c r="J100" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-13700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-22000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-9700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-27800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>-3800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,68 +6847,71 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E101" s="3">
-        <v>400</v>
+        <v>-500</v>
       </c>
       <c r="F101" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="G101" s="3">
+        <v>200</v>
+      </c>
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
-        <v>-400</v>
-      </c>
       <c r="I101" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6672,68 +6921,71 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>10800</v>
+        <v>-10600</v>
       </c>
       <c r="E102" s="3">
-        <v>-23100</v>
+        <v>10900</v>
       </c>
       <c r="F102" s="3">
-        <v>85600</v>
+        <v>-25600</v>
       </c>
       <c r="G102" s="3">
-        <v>5400</v>
+        <v>98100</v>
       </c>
       <c r="H102" s="3">
-        <v>9500</v>
+        <v>6100</v>
       </c>
       <c r="I102" s="3">
-        <v>-6400</v>
+        <v>10900</v>
       </c>
       <c r="J102" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="K102" s="3">
         <v>7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1300</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,104 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,71 +763,74 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E8" s="3">
         <v>21000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,8 +840,11 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -911,35 +917,38 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E10" s="3">
         <v>21000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +994,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,25 +1025,26 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
-        <v>100</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
+      <c r="H12" s="3">
+        <v>300</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -1087,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,35 +1177,38 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6800</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-11900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1235,37 +1254,40 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>900</v>
       </c>
       <c r="J15" s="3">
         <v>900</v>
       </c>
       <c r="K15" s="3">
+        <v>900</v>
+      </c>
+      <c r="L15" s="3">
         <v>800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>700</v>
@@ -1274,32 +1296,32 @@
         <v>700</v>
       </c>
       <c r="O15" s="3">
+        <v>700</v>
+      </c>
+      <c r="P15" s="3">
         <v>800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>700</v>
       </c>
       <c r="Q15" s="3">
         <v>700</v>
       </c>
       <c r="R15" s="3">
+        <v>700</v>
+      </c>
+      <c r="S15" s="3">
         <v>600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2400</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,8 +1331,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,71 +1359,72 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E17" s="3">
         <v>12400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,71 +1434,74 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8600</v>
+        <v>7600</v>
       </c>
       <c r="E18" s="3">
         <v>8600</v>
       </c>
       <c r="F18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="G18" s="3">
         <v>9500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1511,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,71 +1542,72 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-1200</v>
       </c>
       <c r="H20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2900</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3200</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,71 +1617,74 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>11400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>13500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>15500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,25 +1694,28 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3200</v>
+        <v>2900</v>
       </c>
       <c r="E22" s="3">
         <v>3200</v>
       </c>
       <c r="F22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G22" s="3">
         <v>3500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1300</v>
       </c>
       <c r="I22" s="3">
         <v>1300</v>
@@ -1685,19 +1724,19 @@
         <v>1300</v>
       </c>
       <c r="K22" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
       </c>
       <c r="M22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N22" s="3">
         <v>500</v>
       </c>
       <c r="O22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P22" s="3">
         <v>600</v>
@@ -1709,20 +1748,20 @@
         <v>600</v>
       </c>
       <c r="S22" s="3">
+        <v>600</v>
+      </c>
+      <c r="T22" s="3">
         <v>1800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>600</v>
       </c>
       <c r="U22" s="3">
         <v>600</v>
       </c>
       <c r="V22" s="3">
+        <v>600</v>
+      </c>
+      <c r="W22" s="3">
         <v>1700</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,71 +1771,74 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>10100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>23800</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,71 +1848,74 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2100</v>
       </c>
       <c r="F24" s="3">
         <v>2100</v>
       </c>
       <c r="G24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H24" s="3">
         <v>3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2500</v>
       </c>
       <c r="J24" s="3">
         <v>2500</v>
       </c>
       <c r="K24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5900</v>
-      </c>
-      <c r="T24" s="3">
-        <v>2200</v>
       </c>
       <c r="U24" s="3">
         <v>2200</v>
       </c>
       <c r="V24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W24" s="3">
         <v>5000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1880,8 +1925,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,71 +2002,74 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>7600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>9300</v>
       </c>
       <c r="N26" s="3">
         <v>9300</v>
       </c>
       <c r="O26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P26" s="3">
         <v>11600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>22900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>11800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,71 +2079,74 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>9300</v>
       </c>
       <c r="N27" s="3">
         <v>9300</v>
       </c>
       <c r="O27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P27" s="3">
         <v>11600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>22400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,8 +2156,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2233,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2310,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,71 +2464,74 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>1200</v>
       </c>
       <c r="H32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2900</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3200</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,71 +2541,74 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>7700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>9300</v>
       </c>
       <c r="N33" s="3">
         <v>9300</v>
       </c>
       <c r="O33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P33" s="3">
         <v>11600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>22400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2618,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,71 +2695,74 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>7700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>9300</v>
       </c>
       <c r="N35" s="3">
         <v>9300</v>
       </c>
       <c r="O35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P35" s="3">
         <v>11600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>22400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,76 +2772,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2854,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,62 +2914,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E41" s="3">
         <v>98100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>106700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>106100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,35 +2989,38 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>247500</v>
+      </c>
+      <c r="E42" s="3">
         <v>251100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>235600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>243600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>240800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>226500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>245300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>232500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2977,62 +3066,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E43" s="3">
         <v>14900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9500</v>
-      </c>
-      <c r="O43" s="3">
-        <v>9800</v>
       </c>
       <c r="P43" s="3">
         <v>9800</v>
       </c>
       <c r="Q43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="R43" s="3">
         <v>12200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7300</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,8 +3143,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3077,8 +3172,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3125,62 +3220,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>245600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>258600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>270300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>279800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>299800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>292400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>291600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,62 +3297,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>333300</v>
+      </c>
+      <c r="E46" s="3">
         <v>369000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>360800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>373600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>403000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>281900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>295200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>269100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>262000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>270900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>282800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>291200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>314000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>307500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>308500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,62 +3374,65 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E47" s="3">
         <v>13600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,61 +3451,64 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E48" s="3">
         <v>11400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>19700</v>
       </c>
       <c r="S48" s="3">
         <v>19700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3">
+        <v>19700</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3421,43 +3528,46 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E49" s="3">
         <v>42900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>41800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>39000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>40000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>37600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>34500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>200</v>
       </c>
       <c r="O49" s="3">
         <v>200</v>
@@ -3469,13 +3579,13 @@
         <v>200</v>
       </c>
       <c r="R49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S49" s="3">
         <v>300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>300</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3495,8 +3605,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,37 +3759,40 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E52" s="3">
         <v>5200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4100</v>
       </c>
       <c r="G52" s="3">
         <v>4100</v>
       </c>
       <c r="H52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1600</v>
       </c>
       <c r="M52" s="3">
         <v>1600</v>
@@ -3682,23 +3801,23 @@
         <v>1600</v>
       </c>
       <c r="O52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1100</v>
       </c>
       <c r="R52" s="3">
         <v>1100</v>
       </c>
       <c r="S52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3836,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,62 +3913,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>579600</v>
+      </c>
+      <c r="E54" s="3">
         <v>451300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>442300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>452500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>473900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>348900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>358600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>330200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>317600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>325300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>305000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>315300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>338700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>337400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>338400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>61500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3990,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,62 +4050,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1500</v>
       </c>
       <c r="N57" s="3">
         <v>1500</v>
       </c>
       <c r="O57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>23700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,62 +4125,65 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4700</v>
       </c>
       <c r="N58" s="3">
         <v>4700</v>
       </c>
       <c r="O58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P58" s="3">
         <v>4600</v>
-      </c>
-      <c r="P58" s="3">
-        <v>4100</v>
       </c>
       <c r="Q58" s="3">
         <v>4100</v>
       </c>
       <c r="R58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S58" s="3">
         <v>3700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,62 +4202,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E59" s="3">
         <v>6000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,62 +4279,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E60" s="3">
         <v>29100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>48500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17300</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,62 +4356,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E61" s="3">
         <v>123200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>124500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>119200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>121300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>32400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>42900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4291,61 +4433,64 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E62" s="3">
         <v>1200</v>
       </c>
       <c r="F62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>600</v>
       </c>
       <c r="J62" s="3">
         <v>600</v>
       </c>
       <c r="K62" s="3">
+        <v>600</v>
+      </c>
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1900</v>
-      </c>
-      <c r="R62" s="3">
-        <v>2400</v>
       </c>
       <c r="S62" s="3">
         <v>2400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>2400</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -4365,8 +4510,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,62 +4741,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>265600</v>
+      </c>
+      <c r="E66" s="3">
         <v>211000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>201600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>183300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>189400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>82000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>70900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>36500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4818,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4911,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,62 +5155,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E72" s="3">
         <v>14300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12800</v>
-      </c>
-      <c r="K72" s="3">
-        <v>14600</v>
       </c>
       <c r="L72" s="3">
         <v>14600</v>
       </c>
       <c r="M72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="N72" s="3">
         <v>11700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20200</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3">
         <v>22100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5232,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,62 +5463,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>314100</v>
+      </c>
+      <c r="E76" s="3">
         <v>240200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>240600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>268900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>284200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>266400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>282800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>264500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>246700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>255400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>274400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>284000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>290900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>288500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>298300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5540,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,76 +5617,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,71 +5699,74 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>7700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>9300</v>
       </c>
       <c r="N81" s="3">
         <v>9300</v>
       </c>
       <c r="O81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P81" s="3">
         <v>11600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>22400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5582,8 +5776,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,22 +5807,23 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -5637,10 +5835,10 @@
         <v>700</v>
       </c>
       <c r="K83" s="3">
+        <v>700</v>
+      </c>
+      <c r="L83" s="3">
         <v>800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>700</v>
       </c>
       <c r="M83" s="3">
         <v>700</v>
@@ -5649,32 +5847,32 @@
         <v>700</v>
       </c>
       <c r="O83" s="3">
+        <v>700</v>
+      </c>
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2400</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5684,8 +5882,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,71 +6267,74 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L89" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M89" s="3">
         <v>14400</v>
       </c>
-      <c r="H89" s="3">
-        <v>14100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>18100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>8000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>14400</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>15300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>5700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3">
         <v>4600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6128,8 +6344,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,71 +6375,72 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-700</v>
       </c>
       <c r="F91" s="3">
         <v>-700</v>
       </c>
       <c r="G91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,8 +6450,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,71 +6604,74 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E94" s="3">
         <v>30500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-2200</v>
-      </c>
       <c r="H94" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I94" s="3">
         <v>9800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>8500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>11600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>13700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>2000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>12700</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6900</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6681,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,53 +6712,54 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E96" s="3">
         <v>9400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>10600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>9200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>10800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>8900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>9600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-10400</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-9100</v>
       </c>
       <c r="M96" s="3">
         <v>-9100</v>
       </c>
       <c r="N96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="O96" s="3">
         <v>-12100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-10500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6554,8 +6787,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,71 +7018,74 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>86100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>-9700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-27800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
         <v>-3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,71 +7095,74 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6924,71 +7172,74 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-25600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>98100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>-2100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1300</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7247,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,107 +656,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -766,74 +767,77 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E8" s="3">
         <v>39800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>38000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,8 +847,11 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -920,38 +927,41 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E10" s="3">
         <v>39800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -997,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1026,29 +1039,30 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="3">
-        <v>200</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1103,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1180,38 +1197,41 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-6800</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-11900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1257,40 +1277,43 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>900</v>
       </c>
       <c r="L15" s="3">
+        <v>900</v>
+      </c>
+      <c r="M15" s="3">
         <v>800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>700</v>
@@ -1299,32 +1322,32 @@
         <v>700</v>
       </c>
       <c r="P15" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>800</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>700</v>
       </c>
       <c r="R15" s="3">
         <v>700</v>
       </c>
       <c r="S15" s="3">
+        <v>700</v>
+      </c>
+      <c r="T15" s="3">
         <v>600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2400</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1334,8 +1357,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1360,74 +1386,75 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E17" s="3">
         <v>32200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15600</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,74 +1464,77 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>7600</v>
-      </c>
-      <c r="E18" s="3">
-        <v>8600</v>
       </c>
       <c r="F18" s="3">
         <v>8600</v>
       </c>
       <c r="G18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H18" s="3">
         <v>9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>29500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22400</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1514,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1543,74 +1576,75 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-1200</v>
       </c>
       <c r="I20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,74 +1654,77 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E21" s="3">
         <v>6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>13500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>32500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>15500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,28 +1734,31 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3200</v>
       </c>
       <c r="F22" s="3">
         <v>3200</v>
       </c>
       <c r="G22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H22" s="3">
         <v>3500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1300</v>
       </c>
       <c r="J22" s="3">
         <v>1300</v>
@@ -1727,19 +1767,19 @@
         <v>1300</v>
       </c>
       <c r="L22" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="M22" s="3">
         <v>400</v>
       </c>
       <c r="N22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
       </c>
       <c r="P22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q22" s="3">
         <v>600</v>
@@ -1751,20 +1791,20 @@
         <v>600</v>
       </c>
       <c r="T22" s="3">
+        <v>600</v>
+      </c>
+      <c r="U22" s="3">
         <v>1800</v>
-      </c>
-      <c r="U22" s="3">
-        <v>600</v>
       </c>
       <c r="V22" s="3">
         <v>600</v>
       </c>
       <c r="W22" s="3">
+        <v>600</v>
+      </c>
+      <c r="X22" s="3">
         <v>1700</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1774,74 +1814,77 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>23800</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1851,74 +1894,77 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2100</v>
       </c>
       <c r="G24" s="3">
         <v>2100</v>
       </c>
       <c r="H24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I24" s="3">
         <v>3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2500</v>
       </c>
       <c r="K24" s="3">
         <v>2500</v>
       </c>
       <c r="L24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M24" s="3">
         <v>3200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5900</v>
-      </c>
-      <c r="U24" s="3">
-        <v>2200</v>
       </c>
       <c r="V24" s="3">
         <v>2200</v>
       </c>
       <c r="W24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X24" s="3">
         <v>5000</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +1974,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2005,74 +2054,77 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>9300</v>
       </c>
       <c r="O26" s="3">
         <v>9300</v>
       </c>
       <c r="P26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>11600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>22900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18900</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,74 +2134,77 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>9300</v>
       </c>
       <c r="O27" s="3">
         <v>9300</v>
       </c>
       <c r="P27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>11600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>22400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18500</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2159,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2236,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2313,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2390,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2467,74 +2534,77 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>1200</v>
       </c>
       <c r="I32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,74 +2614,77 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>9300</v>
       </c>
       <c r="O33" s="3">
         <v>9300</v>
       </c>
       <c r="P33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>11600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>22400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18500</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2621,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2698,74 +2774,77 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>9300</v>
       </c>
       <c r="O35" s="3">
         <v>9300</v>
       </c>
       <c r="P35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>11600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>22400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18500</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2775,79 +2854,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2886,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2915,65 +3001,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E41" s="3">
         <v>36100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>98100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>106700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>106100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>136100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2992,38 +3079,41 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>259700</v>
+      </c>
+      <c r="E42" s="3">
         <v>247500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>251100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>235600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>243600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>240800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>226500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>245300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>232500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3069,65 +3159,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E43" s="3">
         <v>40700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9500</v>
-      </c>
-      <c r="P43" s="3">
-        <v>9800</v>
       </c>
       <c r="Q43" s="3">
         <v>9800</v>
       </c>
       <c r="R43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="S43" s="3">
         <v>12200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7300</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3146,8 +3239,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3175,8 +3271,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3223,65 +3319,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E45" s="3">
         <v>8900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>245600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>258600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>270300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>279800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>299800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>292400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>291600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3300,65 +3399,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>330400</v>
+      </c>
+      <c r="E46" s="3">
         <v>333300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>369000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>360800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>373600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>403000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>281900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>295200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>269100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>262000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>270900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>282800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>291200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>314000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>307500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>308500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31300</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3479,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3386,56 +3491,56 @@
         <v>32200</v>
       </c>
       <c r="E47" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F47" s="3">
         <v>13600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,64 +3559,67 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E48" s="3">
         <v>26100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>19700</v>
       </c>
       <c r="T48" s="3">
         <v>19700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>19700</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3531,46 +3639,49 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E49" s="3">
         <v>167900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>42900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>41800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>40400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>39000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>37600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>34000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>34500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>200</v>
       </c>
       <c r="P49" s="3">
         <v>200</v>
@@ -3582,13 +3693,13 @@
         <v>200</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T49" s="3">
         <v>300</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>300</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3608,8 +3719,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3685,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3762,40 +3879,43 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E52" s="3">
         <v>8700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4100</v>
       </c>
       <c r="H52" s="3">
         <v>4100</v>
       </c>
       <c r="I52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1600</v>
       </c>
       <c r="N52" s="3">
         <v>1600</v>
@@ -3804,23 +3924,23 @@
         <v>1600</v>
       </c>
       <c r="P52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1100</v>
       </c>
       <c r="S52" s="3">
         <v>1100</v>
       </c>
       <c r="T52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U52" s="3">
         <v>1300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3839,8 +3959,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3916,65 +4039,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>597700</v>
+      </c>
+      <c r="E54" s="3">
         <v>579600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>451300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>442300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>452500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>473900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>348900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>358600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>330200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>317600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>325300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>305000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>315300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>338700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>337400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>338400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>61500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>62500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4022,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4051,65 +4181,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1500</v>
       </c>
       <c r="O57" s="3">
         <v>1500</v>
       </c>
       <c r="P57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>23700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4128,65 +4259,68 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E58" s="3">
         <v>12700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>4700</v>
       </c>
       <c r="O58" s="3">
         <v>4700</v>
       </c>
       <c r="P58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>4600</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>4100</v>
       </c>
       <c r="R58" s="3">
         <v>4100</v>
       </c>
       <c r="S58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T58" s="3">
         <v>3700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4205,65 +4339,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E59" s="3">
         <v>7300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,65 +4419,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E60" s="3">
         <v>56900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>48500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4359,65 +4499,68 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>153400</v>
+      </c>
+      <c r="E61" s="3">
         <v>145900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>124500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>119200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>121300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>32400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4436,8 +4579,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4445,55 +4591,55 @@
         <v>1500</v>
       </c>
       <c r="E62" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F62" s="3">
         <v>1200</v>
       </c>
       <c r="G62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>600</v>
       </c>
       <c r="K62" s="3">
         <v>600</v>
       </c>
       <c r="L62" s="3">
+        <v>600</v>
+      </c>
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>2400</v>
       </c>
       <c r="T62" s="3">
         <v>2400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>2400</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4513,8 +4659,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4590,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4667,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4744,65 +4899,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E66" s="3">
         <v>265600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>211000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>201600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>183300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>189400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>65100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>70900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>69800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>40000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>36500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4821,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4850,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4927,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5004,8 +5169,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5081,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5158,65 +5329,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12800</v>
-      </c>
-      <c r="L72" s="3">
-        <v>14600</v>
       </c>
       <c r="M72" s="3">
         <v>14600</v>
       </c>
       <c r="N72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="O72" s="3">
         <v>11700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20200</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3">
         <v>22100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5235,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5312,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5389,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5466,65 +5649,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>329700</v>
+      </c>
+      <c r="E76" s="3">
         <v>314100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>240200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>240600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>268900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>284200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>266400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>282800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>264500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>246700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>255400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>274400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>284000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>290900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>288500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>298300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5543,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5620,79 +5809,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5702,74 +5894,77 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>9300</v>
       </c>
       <c r="O81" s="3">
         <v>9300</v>
       </c>
       <c r="P81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>11600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>22400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18500</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5779,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5808,25 +6006,26 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>700</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
@@ -5838,10 +6037,10 @@
         <v>700</v>
       </c>
       <c r="L83" s="3">
+        <v>700</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
@@ -5850,32 +6049,32 @@
         <v>700</v>
       </c>
       <c r="P83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2400</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5885,8 +6084,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5962,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6039,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6116,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6193,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6270,74 +6484,77 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28300</v>
       </c>
-      <c r="G89" s="3">
-        <v>23600</v>
-      </c>
       <c r="H89" s="3">
+        <v>12100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>23900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>5700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>32200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3">
         <v>4600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6347,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6376,74 +6596,75 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-700</v>
       </c>
       <c r="G91" s="3">
         <v>-700</v>
       </c>
       <c r="H91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6453,8 +6674,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6530,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6607,74 +6834,77 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>30500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-28100</v>
-      </c>
       <c r="H94" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="I94" s="3">
         <v>15300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>9800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>8500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>13700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>2000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>12700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6900</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6684,8 +6914,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6713,56 +6946,57 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E96" s="3">
         <v>8200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>10600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>9200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>10800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>8900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>9600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-10400</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-9100</v>
       </c>
       <c r="N96" s="3">
         <v>-9100</v>
       </c>
       <c r="O96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="P96" s="3">
         <v>-12100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-17900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6790,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6867,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6944,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7021,74 +7264,77 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>86100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-22000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>-9700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-27800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>-3800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7098,74 +7344,77 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7175,74 +7424,77 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-50300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>98100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>17800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7250,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,111 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -770,77 +771,80 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E8" s="3">
         <v>40900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>39800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>23700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>46000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>38000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,8 +854,11 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -930,41 +937,44 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E10" s="3">
         <v>40900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>39800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,8 +1020,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,32 +1053,33 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,8 +1134,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,41 +1217,44 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-6800</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-11900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1280,43 +1300,46 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3">
         <v>2400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>900</v>
       </c>
       <c r="L15" s="3">
         <v>900</v>
       </c>
       <c r="M15" s="3">
+        <v>900</v>
+      </c>
+      <c r="N15" s="3">
         <v>800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>700</v>
       </c>
       <c r="O15" s="3">
         <v>700</v>
@@ -1325,32 +1348,32 @@
         <v>700</v>
       </c>
       <c r="Q15" s="3">
+        <v>700</v>
+      </c>
+      <c r="R15" s="3">
         <v>800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>700</v>
       </c>
       <c r="S15" s="3">
         <v>700</v>
       </c>
       <c r="T15" s="3">
+        <v>700</v>
+      </c>
+      <c r="U15" s="3">
         <v>600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2400</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,8 +1383,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,77 +1413,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E17" s="3">
         <v>30600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,77 +1494,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E18" s="3">
         <v>10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>8600</v>
       </c>
       <c r="G18" s="3">
         <v>8600</v>
       </c>
       <c r="H18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I18" s="3">
         <v>9500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>29500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>22400</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1577,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1577,77 +1610,78 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>-1200</v>
       </c>
       <c r="J20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,77 +1691,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E21" s="3">
         <v>12700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>13500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>32500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>15500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1774,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1746,22 +1786,22 @@
         <v>3500</v>
       </c>
       <c r="E22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F22" s="3">
         <v>2900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3200</v>
       </c>
       <c r="G22" s="3">
         <v>3200</v>
       </c>
       <c r="H22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1300</v>
       </c>
       <c r="K22" s="3">
         <v>1300</v>
@@ -1770,19 +1810,19 @@
         <v>1300</v>
       </c>
       <c r="M22" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="N22" s="3">
         <v>400</v>
       </c>
       <c r="O22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P22" s="3">
         <v>500</v>
       </c>
       <c r="Q22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R22" s="3">
         <v>600</v>
@@ -1794,20 +1834,20 @@
         <v>600</v>
       </c>
       <c r="U22" s="3">
+        <v>600</v>
+      </c>
+      <c r="V22" s="3">
         <v>1800</v>
-      </c>
-      <c r="V22" s="3">
-        <v>600</v>
       </c>
       <c r="W22" s="3">
         <v>600</v>
       </c>
       <c r="X22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1700</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,77 +1857,80 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E23" s="3">
         <v>11700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>28800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>11200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>14000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>23800</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1897,77 +1940,80 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2100</v>
       </c>
       <c r="H24" s="3">
         <v>2100</v>
       </c>
       <c r="I24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J24" s="3">
         <v>3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2500</v>
       </c>
       <c r="L24" s="3">
         <v>2500</v>
       </c>
       <c r="M24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5900</v>
-      </c>
-      <c r="V24" s="3">
-        <v>2200</v>
       </c>
       <c r="W24" s="3">
         <v>2200</v>
       </c>
       <c r="X24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Y24" s="3">
         <v>5000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1977,8 +2023,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,77 +2106,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E26" s="3">
         <v>9800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>9300</v>
       </c>
       <c r="P26" s="3">
         <v>9300</v>
       </c>
       <c r="Q26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R26" s="3">
         <v>11600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>22900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2137,77 +2189,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E27" s="3">
         <v>9900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>9300</v>
       </c>
       <c r="P27" s="3">
         <v>9300</v>
       </c>
       <c r="Q27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R27" s="3">
         <v>11600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>22400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,8 +2272,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2355,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2377,8 +2438,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2521,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,77 +2604,80 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>1200</v>
       </c>
       <c r="J32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,77 +2687,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E33" s="3">
         <v>9900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12800</v>
-      </c>
-      <c r="O33" s="3">
-        <v>9300</v>
       </c>
       <c r="P33" s="3">
         <v>9300</v>
       </c>
       <c r="Q33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R33" s="3">
         <v>11600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>22400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2770,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,77 +2853,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E35" s="3">
         <v>9900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12800</v>
-      </c>
-      <c r="O35" s="3">
-        <v>9300</v>
       </c>
       <c r="P35" s="3">
         <v>9300</v>
       </c>
       <c r="Q35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R35" s="3">
         <v>11600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>22400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,82 +2936,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2942,8 +3024,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3057,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,68 +3088,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E41" s="3">
         <v>28600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>98100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>106700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>106100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>136100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3082,41 +3169,44 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>266100</v>
+      </c>
+      <c r="E42" s="3">
         <v>259700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>247500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>251100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>235600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>243600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>240800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>226500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>245300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>232500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3162,68 +3252,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E43" s="3">
         <v>30600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>40700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9500</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>9800</v>
       </c>
       <c r="R43" s="3">
         <v>9800</v>
       </c>
       <c r="S43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="T43" s="3">
         <v>12200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7300</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3242,8 +3335,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,8 +3370,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3322,68 +3418,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E45" s="3">
         <v>11600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>245600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>258600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>270300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>279800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>299800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>292400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>291600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>21300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3402,68 +3501,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>348400</v>
+      </c>
+      <c r="E46" s="3">
         <v>330400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>333300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>369000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>360800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>373600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>403000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>281900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>295200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>269100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>262000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>270900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>282800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>291200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>314000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>307500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>308500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>29200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>31300</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,68 +3584,71 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>32200</v>
+        <v>36200</v>
       </c>
       <c r="E47" s="3">
         <v>32200</v>
       </c>
       <c r="F47" s="3">
+        <v>32200</v>
+      </c>
+      <c r="G47" s="3">
         <v>13600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9800</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3562,67 +3667,70 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E48" s="3">
         <v>34200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>19700</v>
       </c>
       <c r="U48" s="3">
         <v>19700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>19700</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3642,49 +3750,52 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E49" s="3">
         <v>180700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>167900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>42900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>41800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>39300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>40400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>39000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>40000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>37600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>34000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>34500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>200</v>
       </c>
       <c r="Q49" s="3">
         <v>200</v>
@@ -3696,13 +3807,13 @@
         <v>200</v>
       </c>
       <c r="T49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U49" s="3">
         <v>300</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>300</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3722,8 +3833,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +3916,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,43 +3999,46 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E52" s="3">
         <v>8300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>4100</v>
       </c>
       <c r="I52" s="3">
         <v>4100</v>
       </c>
       <c r="J52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1600</v>
       </c>
       <c r="O52" s="3">
         <v>1600</v>
@@ -3927,23 +4047,23 @@
         <v>1600</v>
       </c>
       <c r="Q52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R52" s="3">
         <v>1400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1500</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1100</v>
       </c>
       <c r="T52" s="3">
         <v>1100</v>
       </c>
       <c r="U52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V52" s="3">
         <v>1300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3962,8 +4082,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,68 +4165,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>628000</v>
+      </c>
+      <c r="E54" s="3">
         <v>597700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>579600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>451300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>442300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>452500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>473900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>348900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>358600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>330200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>317600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>325300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>305000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>315300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>338700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>337400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>338400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>61500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>62500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4122,8 +4248,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4281,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,68 +4312,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
       <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1500</v>
       </c>
       <c r="P57" s="3">
         <v>1500</v>
       </c>
       <c r="Q57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>23700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4262,68 +4393,71 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E58" s="3">
         <v>10900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>4700</v>
       </c>
       <c r="P58" s="3">
         <v>4700</v>
       </c>
       <c r="Q58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="R58" s="3">
         <v>4600</v>
-      </c>
-      <c r="R58" s="3">
-        <v>4100</v>
       </c>
       <c r="S58" s="3">
         <v>4100</v>
       </c>
       <c r="T58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="U58" s="3">
         <v>3700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,68 +4476,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E59" s="3">
         <v>10100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4422,68 +4559,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E60" s="3">
         <v>39800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>56900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>48500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>33700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17300</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,68 +4642,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>152900</v>
+      </c>
+      <c r="E61" s="3">
         <v>153400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>145900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>123200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>124500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>119200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>121300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>32400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15900</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4582,67 +4725,70 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
         <v>1500</v>
       </c>
       <c r="F62" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="G62" s="3">
         <v>1200</v>
       </c>
       <c r="H62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I62" s="3">
         <v>1400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
-      </c>
-      <c r="K62" s="3">
-        <v>600</v>
       </c>
       <c r="L62" s="3">
         <v>600</v>
       </c>
       <c r="M62" s="3">
+        <v>600</v>
+      </c>
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1900</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2400</v>
       </c>
       <c r="U62" s="3">
         <v>2400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>2400</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -4662,8 +4808,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +4891,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +4974,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,68 +5057,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>282400</v>
+      </c>
+      <c r="E66" s="3">
         <v>268100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>265600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>211000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>201600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>183300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>189400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>75200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>70900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>69800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>48900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>40000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>36500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,8 +5140,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5173,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5254,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,8 +5337,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5252,8 +5420,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,68 +5503,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E72" s="3">
         <v>15200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12800</v>
-      </c>
-      <c r="M72" s="3">
-        <v>14600</v>
       </c>
       <c r="N72" s="3">
         <v>14600</v>
       </c>
       <c r="O72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="P72" s="3">
         <v>11700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20200</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
       <c r="U72" s="3">
+        <v>0</v>
+      </c>
+      <c r="V72" s="3">
         <v>22100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,8 +5586,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5669,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5752,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,68 +5835,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>345900</v>
+      </c>
+      <c r="E76" s="3">
         <v>329700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>314100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>240200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>240600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>268900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>284200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>266400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>282800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>264500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>246700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>255400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>274400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>284000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>290900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>288500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>298300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5732,8 +5918,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,82 +6001,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5897,77 +6089,80 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E81" s="3">
         <v>9900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12800</v>
-      </c>
-      <c r="O81" s="3">
-        <v>9300</v>
       </c>
       <c r="P81" s="3">
         <v>9300</v>
       </c>
       <c r="Q81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="R81" s="3">
         <v>11600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>22400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,8 +6172,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,28 +6205,29 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>700</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
@@ -6040,10 +6239,10 @@
         <v>700</v>
       </c>
       <c r="M83" s="3">
+        <v>700</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>700</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
@@ -6052,32 +6251,32 @@
         <v>700</v>
       </c>
       <c r="Q83" s="3">
+        <v>700</v>
+      </c>
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1900</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6087,8 +6286,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6369,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6452,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6535,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6618,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,77 +6701,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E89" s="3">
         <v>2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12700</v>
       </c>
-      <c r="G89" s="3">
-        <v>28300</v>
-      </c>
       <c r="H89" s="3">
+        <v>12300</v>
+      </c>
+      <c r="I89" s="3">
         <v>12100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>5700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>32200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3">
         <v>4600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6567,8 +6784,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,77 +6817,78 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-700</v>
       </c>
       <c r="H91" s="3">
         <v>-700</v>
       </c>
       <c r="I91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6898,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +6981,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,77 +7064,80 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>11500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-36000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>30500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H94" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-16500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>8500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>11600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>13700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>2000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>12700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6917,8 +7147,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,59 +7180,60 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E96" s="3">
         <v>9500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>9400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>10600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>9200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>10800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>8900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>9600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-10400</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-9100</v>
       </c>
       <c r="O96" s="3">
         <v>-9100</v>
       </c>
       <c r="P96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-10500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-17900</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -7027,8 +7261,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7344,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7427,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,77 +7510,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-23300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>86100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-22000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>-9700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-27800</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>-3800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7347,77 +7593,80 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7427,77 +7676,80 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-50300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>98100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-2100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7505,6 +7757,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,115 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -774,80 +775,83 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E8" s="3">
         <v>44200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>39800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>24100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>46000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>38000</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,8 +861,11 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -940,44 +947,47 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E10" s="3">
         <v>44200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>40900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20200</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,35 +1067,36 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3">
+        <v>400</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1137,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,44 +1237,47 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-6800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-11900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1303,8 +1323,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,37 +1335,37 @@
         <v>2700</v>
       </c>
       <c r="E15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F15" s="3">
         <v>2400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>900</v>
       </c>
       <c r="M15" s="3">
         <v>900</v>
       </c>
       <c r="N15" s="3">
+        <v>900</v>
+      </c>
+      <c r="O15" s="3">
         <v>800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>700</v>
       </c>
       <c r="P15" s="3">
         <v>700</v>
@@ -1351,32 +1374,32 @@
         <v>700</v>
       </c>
       <c r="R15" s="3">
+        <v>700</v>
+      </c>
+      <c r="S15" s="3">
         <v>800</v>
-      </c>
-      <c r="S15" s="3">
-        <v>700</v>
       </c>
       <c r="T15" s="3">
         <v>700</v>
       </c>
       <c r="U15" s="3">
+        <v>700</v>
+      </c>
+      <c r="V15" s="3">
         <v>600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2400</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,8 +1409,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1414,80 +1440,81 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E17" s="3">
         <v>33500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>30600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15600</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,80 +1524,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E18" s="3">
         <v>10800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>8600</v>
       </c>
       <c r="H18" s="3">
         <v>8600</v>
       </c>
       <c r="I18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J18" s="3">
         <v>9500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>29500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>22400</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,80 +1644,81 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-1200</v>
       </c>
       <c r="K20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3200</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1694,80 +1728,83 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E21" s="3">
         <v>12300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>16000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>13500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>32500</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>15500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,34 +1814,37 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="E22" s="3">
         <v>3500</v>
       </c>
       <c r="F22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G22" s="3">
         <v>2900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3200</v>
       </c>
       <c r="H22" s="3">
         <v>3200</v>
       </c>
       <c r="I22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1300</v>
       </c>
       <c r="L22" s="3">
         <v>1300</v>
@@ -1813,19 +1853,19 @@
         <v>1300</v>
       </c>
       <c r="N22" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
       </c>
       <c r="P22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q22" s="3">
         <v>500</v>
       </c>
       <c r="R22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S22" s="3">
         <v>600</v>
@@ -1837,20 +1877,20 @@
         <v>600</v>
       </c>
       <c r="V22" s="3">
+        <v>600</v>
+      </c>
+      <c r="W22" s="3">
         <v>1800</v>
-      </c>
-      <c r="W22" s="3">
-        <v>600</v>
       </c>
       <c r="X22" s="3">
         <v>600</v>
       </c>
       <c r="Y22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z22" s="3">
         <v>1700</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1860,80 +1900,83 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E23" s="3">
         <v>14500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>11200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>14000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>23800</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,80 +1986,83 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>2100</v>
       </c>
       <c r="I24" s="3">
         <v>2100</v>
       </c>
       <c r="J24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>2500</v>
       </c>
       <c r="M24" s="3">
         <v>2500</v>
       </c>
       <c r="N24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>2200</v>
       </c>
       <c r="X24" s="3">
         <v>2200</v>
       </c>
       <c r="Y24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>5000</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,8 +2072,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2109,80 +2158,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E26" s="3">
         <v>12300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12800</v>
-      </c>
-      <c r="P26" s="3">
-        <v>9300</v>
       </c>
       <c r="Q26" s="3">
         <v>9300</v>
       </c>
       <c r="R26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S26" s="3">
         <v>11600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>11800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18900</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,80 +2244,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>12400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12800</v>
-      </c>
-      <c r="P27" s="3">
-        <v>9300</v>
       </c>
       <c r="Q27" s="3">
         <v>9300</v>
       </c>
       <c r="R27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S27" s="3">
         <v>11600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>22400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18500</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2358,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2524,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2607,80 +2674,83 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>1200</v>
       </c>
       <c r="K32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,80 +2760,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>12400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12800</v>
-      </c>
-      <c r="P33" s="3">
-        <v>9300</v>
       </c>
       <c r="Q33" s="3">
         <v>9300</v>
       </c>
       <c r="R33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S33" s="3">
         <v>11600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18500</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2856,80 +2932,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>12400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12800</v>
-      </c>
-      <c r="P35" s="3">
-        <v>9300</v>
       </c>
       <c r="Q35" s="3">
         <v>9300</v>
       </c>
       <c r="R35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S35" s="3">
         <v>11600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18500</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,85 +3018,88 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3058,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3089,71 +3175,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E41" s="3">
         <v>34700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>98100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>106700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>106100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,44 +3259,47 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>278600</v>
+      </c>
+      <c r="E42" s="3">
         <v>266100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>259700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>247500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>251100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>235600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>243600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>240800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>226500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>245300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>232500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -3255,71 +3345,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E43" s="3">
         <v>37100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9500</v>
-      </c>
-      <c r="R43" s="3">
-        <v>9800</v>
       </c>
       <c r="S43" s="3">
         <v>9800</v>
       </c>
       <c r="T43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="U43" s="3">
         <v>12200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7300</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3338,8 +3431,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3373,8 +3469,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3421,71 +3517,74 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E45" s="3">
         <v>10600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>245600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>258600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>270300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>279800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>299800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>292400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>291600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>21300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,71 +3603,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>384800</v>
+      </c>
+      <c r="E46" s="3">
         <v>348400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>330400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>333300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>369000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>360800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>373600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>403000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>281900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>295200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>269100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>262000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>270900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>282800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>291200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>314000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>307500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>308500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>29200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,71 +3689,74 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E47" s="3">
         <v>36200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>32200</v>
       </c>
       <c r="F47" s="3">
         <v>32200</v>
       </c>
       <c r="G47" s="3">
+        <v>32200</v>
+      </c>
+      <c r="H47" s="3">
         <v>13600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,70 +3775,73 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E48" s="3">
         <v>35200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20600</v>
-      </c>
-      <c r="U48" s="3">
-        <v>19700</v>
       </c>
       <c r="V48" s="3">
         <v>19700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>19700</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3753,52 +3861,55 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>237600</v>
+      </c>
+      <c r="E49" s="3">
         <v>189800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>180700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>167900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>41800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>39300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>39000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>40000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>34000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>34500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>300</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>200</v>
       </c>
       <c r="R49" s="3">
         <v>200</v>
@@ -3810,13 +3921,13 @@
         <v>200</v>
       </c>
       <c r="U49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V49" s="3">
         <v>300</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>300</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3836,8 +3947,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3919,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,46 +4119,49 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>4100</v>
       </c>
       <c r="J52" s="3">
         <v>4100</v>
       </c>
       <c r="K52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1600</v>
       </c>
       <c r="P52" s="3">
         <v>1600</v>
@@ -4050,23 +4170,23 @@
         <v>1600</v>
       </c>
       <c r="R52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S52" s="3">
         <v>1400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1100</v>
       </c>
       <c r="U52" s="3">
         <v>1100</v>
       </c>
       <c r="V52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W52" s="3">
         <v>1300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4085,8 +4205,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4168,71 +4291,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>732200</v>
+      </c>
+      <c r="E54" s="3">
         <v>628000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>597700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>579600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>451300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>442300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>452500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>473900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>348900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>358600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>330200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>317600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>325300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>305000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>315300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>338700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>337400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>338400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>61500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>62500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4251,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4282,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4313,71 +4443,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1500</v>
       </c>
       <c r="Q57" s="3">
         <v>1500</v>
       </c>
       <c r="R57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>23700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,71 +4527,74 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E58" s="3">
         <v>10600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>4700</v>
       </c>
       <c r="Q58" s="3">
         <v>4700</v>
       </c>
       <c r="R58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S58" s="3">
         <v>4600</v>
-      </c>
-      <c r="S58" s="3">
-        <v>4100</v>
       </c>
       <c r="T58" s="3">
         <v>4100</v>
       </c>
       <c r="U58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="V58" s="3">
         <v>3700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4479,71 +4613,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E59" s="3">
         <v>7800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4562,71 +4699,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E60" s="3">
         <v>44400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>48500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>33700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4645,71 +4785,74 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>181500</v>
+      </c>
+      <c r="E61" s="3">
         <v>152900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>153400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>145900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>123200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>124500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>119200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>121300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>32400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>40300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4728,70 +4871,73 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1500</v>
       </c>
       <c r="F62" s="3">
         <v>1500</v>
       </c>
       <c r="G62" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="H62" s="3">
         <v>1200</v>
       </c>
       <c r="I62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J62" s="3">
         <v>1400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>600</v>
       </c>
       <c r="M62" s="3">
         <v>600</v>
       </c>
       <c r="N62" s="3">
+        <v>600</v>
+      </c>
+      <c r="O62" s="3">
         <v>2000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1900</v>
-      </c>
-      <c r="U62" s="3">
-        <v>2400</v>
       </c>
       <c r="V62" s="3">
         <v>2400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="W62" s="3">
+        <v>2400</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -4811,8 +4957,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4894,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4977,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5060,71 +5215,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>359400</v>
+      </c>
+      <c r="E66" s="3">
         <v>282400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>268100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>265600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>211000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>201600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>183300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>189400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>65100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>70900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>57900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5143,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5174,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5257,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5340,8 +5505,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5423,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5506,71 +5677,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E72" s="3">
         <v>18600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12800</v>
-      </c>
-      <c r="N72" s="3">
-        <v>14600</v>
       </c>
       <c r="O72" s="3">
         <v>14600</v>
       </c>
       <c r="P72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="Q72" s="3">
         <v>11700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20200</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
       <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="W72" s="3">
         <v>22100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5589,8 +5763,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5672,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5755,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5838,71 +6021,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>359300</v>
+      </c>
+      <c r="E76" s="3">
         <v>345900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>329700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>314100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>240200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>240600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>268900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>284200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>266400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>282800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>264500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>246700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>255400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>274400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>284000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>290900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>288500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>298300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>26000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5921,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6004,85 +6193,88 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6092,80 +6284,83 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>12400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12800</v>
-      </c>
-      <c r="P81" s="3">
-        <v>9300</v>
       </c>
       <c r="Q81" s="3">
         <v>9300</v>
       </c>
       <c r="R81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S81" s="3">
         <v>11600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18500</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6175,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6206,31 +6404,32 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
@@ -6242,10 +6441,10 @@
         <v>700</v>
       </c>
       <c r="N83" s="3">
+        <v>700</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
@@ -6254,32 +6453,32 @@
         <v>700</v>
       </c>
       <c r="R83" s="3">
+        <v>700</v>
+      </c>
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1900</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3">
         <v>800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6289,8 +6488,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6372,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6455,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6538,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6621,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6704,80 +6918,83 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>15300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>23900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3">
         <v>5700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3">
         <v>4600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6787,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6818,80 +7038,81 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-700</v>
       </c>
       <c r="I91" s="3">
         <v>-700</v>
       </c>
       <c r="J91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6901,8 +7122,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6984,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7067,80 +7294,83 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>7000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-36000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>30500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>9800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>15300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>8500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>13700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
         <v>2000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>12700</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7150,8 +7380,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7181,62 +7414,63 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E96" s="3">
         <v>9700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>9400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>8600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>10600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>9200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>10800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>8900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>9600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-10400</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-9100</v>
       </c>
       <c r="P96" s="3">
         <v>-9100</v>
       </c>
       <c r="Q96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="R96" s="3">
         <v>-12100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-10500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-17900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -7264,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7347,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7430,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7513,80 +7756,83 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-23300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-28400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>86100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-22000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
         <v>-9700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-27800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7596,80 +7842,83 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7679,80 +7928,83 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E102" s="3">
         <v>4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-50300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>98100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3">
         <v>-2100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7760,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VINP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>VINP</t>
   </si>
@@ -656,119 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -778,83 +779,86 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E8" s="3">
         <v>47300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>44200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>40900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>39800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>24900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>19600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>46000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>38000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,8 +868,11 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -950,47 +957,50 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E10" s="3">
         <v>47300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>44200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>40900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1046,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,38 +1081,39 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>800</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1168,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,47 +1257,50 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-8400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-6800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-11900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1326,49 +1346,52 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2700</v>
+        <v>3300</v>
       </c>
       <c r="E15" s="3">
         <v>2700</v>
       </c>
       <c r="F15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G15" s="3">
         <v>2400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1200</v>
-      </c>
-      <c r="M15" s="3">
-        <v>900</v>
       </c>
       <c r="N15" s="3">
         <v>900</v>
       </c>
       <c r="O15" s="3">
+        <v>900</v>
+      </c>
+      <c r="P15" s="3">
         <v>800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>700</v>
       </c>
       <c r="Q15" s="3">
         <v>700</v>
@@ -1377,32 +1400,32 @@
         <v>700</v>
       </c>
       <c r="S15" s="3">
+        <v>700</v>
+      </c>
+      <c r="T15" s="3">
         <v>800</v>
-      </c>
-      <c r="T15" s="3">
-        <v>700</v>
       </c>
       <c r="U15" s="3">
         <v>700</v>
       </c>
       <c r="V15" s="3">
+        <v>700</v>
+      </c>
+      <c r="W15" s="3">
         <v>600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2400</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1412,8 +1435,11 @@
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,83 +1467,84 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E17" s="3">
         <v>35100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15600</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1527,83 +1554,86 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E18" s="3">
         <v>12200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>8600</v>
       </c>
       <c r="I18" s="3">
         <v>8600</v>
       </c>
       <c r="J18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K18" s="3">
         <v>9500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>29500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>22400</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1613,8 +1643,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,83 +1678,84 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-1200</v>
       </c>
       <c r="L20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3200</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,83 +1765,86 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>13500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>32500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>15500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,37 +1854,40 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E22" s="3">
         <v>3400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3500</v>
       </c>
       <c r="F22" s="3">
         <v>3500</v>
       </c>
       <c r="G22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H22" s="3">
         <v>2900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>3200</v>
       </c>
       <c r="I22" s="3">
         <v>3200</v>
       </c>
       <c r="J22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1300</v>
       </c>
       <c r="M22" s="3">
         <v>1300</v>
@@ -1856,19 +1896,19 @@
         <v>1300</v>
       </c>
       <c r="O22" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
       </c>
       <c r="Q22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R22" s="3">
         <v>500</v>
       </c>
       <c r="S22" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T22" s="3">
         <v>600</v>
@@ -1880,20 +1920,20 @@
         <v>600</v>
       </c>
       <c r="W22" s="3">
+        <v>600</v>
+      </c>
+      <c r="X22" s="3">
         <v>1800</v>
-      </c>
-      <c r="X22" s="3">
-        <v>600</v>
       </c>
       <c r="Y22" s="3">
         <v>600</v>
       </c>
       <c r="Z22" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1700</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,83 +1943,86 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E23" s="3">
         <v>9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>28800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>11200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>23800</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,83 +2032,86 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2100</v>
       </c>
       <c r="J24" s="3">
         <v>2100</v>
       </c>
       <c r="K24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2500</v>
       </c>
       <c r="N24" s="3">
         <v>2500</v>
       </c>
       <c r="O24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5900</v>
-      </c>
-      <c r="X24" s="3">
-        <v>2200</v>
       </c>
       <c r="Y24" s="3">
         <v>2200</v>
       </c>
       <c r="Z24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA24" s="3">
         <v>5000</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2075,8 +2121,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2161,83 +2210,86 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12800</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>9300</v>
       </c>
       <c r="R26" s="3">
         <v>9300</v>
       </c>
       <c r="S26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T26" s="3">
         <v>11600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>22900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18900</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,83 +2299,86 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E27" s="3">
         <v>8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12800</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>9300</v>
       </c>
       <c r="R27" s="3">
         <v>9300</v>
       </c>
       <c r="S27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T27" s="3">
         <v>11600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>22400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,8 +2388,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,8 +2477,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2505,8 +2566,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2591,8 +2655,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2677,83 +2744,86 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>1200</v>
       </c>
       <c r="L32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,83 +2833,86 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E33" s="3">
         <v>8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12800</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>9300</v>
       </c>
       <c r="R33" s="3">
         <v>9300</v>
       </c>
       <c r="S33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T33" s="3">
         <v>11600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>22400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2849,8 +2922,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2935,83 +3011,86 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E35" s="3">
         <v>8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12800</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>9300</v>
       </c>
       <c r="R35" s="3">
         <v>9300</v>
       </c>
       <c r="S35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T35" s="3">
         <v>11600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>22400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3021,88 +3100,91 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3194,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,8 +3229,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,74 +3262,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E41" s="3">
         <v>50900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>98100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>106700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>106100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>136100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3262,47 +3349,50 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E42" s="3">
         <v>278600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>266100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>259700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>247500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>251100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>235600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>243600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>240800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>226500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>245300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>232500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3348,74 +3438,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E43" s="3">
         <v>42600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>37100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9500</v>
-      </c>
-      <c r="S43" s="3">
-        <v>9800</v>
       </c>
       <c r="T43" s="3">
         <v>9800</v>
       </c>
       <c r="U43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="V43" s="3">
         <v>12200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7300</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3434,8 +3527,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3472,8 +3568,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3520,74 +3616,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E45" s="3">
         <v>12700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>245600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>258600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>270300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>279800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>299800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>292400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>291600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,74 +3705,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E46" s="3">
         <v>384800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>348400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>330400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>333300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>369000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>360800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>373600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>403000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>281900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>295200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>269100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>262000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>270900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>282800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>291200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>314000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>307500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>308500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>29200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>31300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3692,74 +3794,77 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>183400</v>
+      </c>
+      <c r="E47" s="3">
         <v>40000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>36200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>32200</v>
       </c>
       <c r="G47" s="3">
         <v>32200</v>
       </c>
       <c r="H47" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I47" s="3">
         <v>13600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3778,73 +3883,76 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E48" s="3">
         <v>39100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>19700</v>
       </c>
       <c r="W48" s="3">
         <v>19700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="X48" s="3">
+        <v>19700</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3864,55 +3972,58 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>249700</v>
+      </c>
+      <c r="E49" s="3">
         <v>237600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>189800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>180700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>167900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>41800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>39300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>40400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>39000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>40000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>37600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>34000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>34500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>300</v>
-      </c>
-      <c r="R49" s="3">
-        <v>200</v>
       </c>
       <c r="S49" s="3">
         <v>200</v>
@@ -3924,13 +4035,13 @@
         <v>200</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>300</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -3950,8 +4061,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4036,8 +4150,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4122,49 +4239,52 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E52" s="3">
         <v>15700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>4100</v>
       </c>
       <c r="K52" s="3">
         <v>4100</v>
       </c>
       <c r="L52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1600</v>
       </c>
       <c r="Q52" s="3">
         <v>1600</v>
@@ -4173,23 +4293,23 @@
         <v>1600</v>
       </c>
       <c r="S52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T52" s="3">
         <v>1400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1100</v>
       </c>
       <c r="V52" s="3">
         <v>1100</v>
       </c>
       <c r="W52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X52" s="3">
         <v>1300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,8 +4328,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4294,74 +4417,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>746400</v>
+      </c>
+      <c r="E54" s="3">
         <v>732200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>628000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>597700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>579600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>451300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>442300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>452500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>473900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>348900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>358600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>330200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>317600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>325300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>305000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>315300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>338700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>337400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>338400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>61500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>62500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4380,8 +4506,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,8 +4541,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,74 +4574,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1500</v>
       </c>
       <c r="R57" s="3">
         <v>1500</v>
       </c>
       <c r="S57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>23700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,74 +4661,77 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E58" s="3">
         <v>23100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>4700</v>
       </c>
       <c r="R58" s="3">
         <v>4700</v>
       </c>
       <c r="S58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T58" s="3">
         <v>4600</v>
-      </c>
-      <c r="T58" s="3">
-        <v>4100</v>
       </c>
       <c r="U58" s="3">
         <v>4100</v>
       </c>
       <c r="V58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W58" s="3">
         <v>3700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4616,74 +4750,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13200</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,74 +4839,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E60" s="3">
         <v>75000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>39800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>56900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>48500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,74 +4928,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>185900</v>
+      </c>
+      <c r="E61" s="3">
         <v>181500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>152900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>153400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>145900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>123200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>124500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>119200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>121300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>32400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>44000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4874,73 +5017,76 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E62" s="3">
         <v>9700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1500</v>
       </c>
       <c r="G62" s="3">
         <v>1500</v>
       </c>
       <c r="H62" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="I62" s="3">
         <v>1200</v>
       </c>
       <c r="J62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>600</v>
       </c>
       <c r="N62" s="3">
         <v>600</v>
       </c>
       <c r="O62" s="3">
+        <v>600</v>
+      </c>
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1900</v>
-      </c>
-      <c r="V62" s="3">
-        <v>2400</v>
       </c>
       <c r="W62" s="3">
         <v>2400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+      <c r="X62" s="3">
+        <v>2400</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
@@ -4960,8 +5106,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5046,8 +5195,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5132,8 +5284,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5218,74 +5373,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>346400</v>
+      </c>
+      <c r="E66" s="3">
         <v>359400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>282400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>268100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>265600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>211000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>201600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>183300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>189400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>65100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>70900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>40000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5304,8 +5462,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,8 +5497,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5422,8 +5584,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5508,8 +5673,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5594,8 +5762,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5680,74 +5851,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E72" s="3">
         <v>16700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12800</v>
-      </c>
-      <c r="O72" s="3">
-        <v>14600</v>
       </c>
       <c r="P72" s="3">
         <v>14600</v>
       </c>
       <c r="Q72" s="3">
+        <v>14600</v>
+      </c>
+      <c r="R72" s="3">
         <v>11700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20200</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
       <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
         <v>22100</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5766,8 +5940,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5852,8 +6029,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5938,8 +6118,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6024,74 +6207,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>385000</v>
+      </c>
+      <c r="E76" s="3">
         <v>359300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>345900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>329700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>314100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>240200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>240600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>268900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>284200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>266400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>282800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>264500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>246700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>255400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>274400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>284000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>290900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>288500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>298300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6110,8 +6296,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6196,88 +6385,91 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6287,83 +6479,86 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E81" s="3">
         <v>8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12800</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>9300</v>
       </c>
       <c r="R81" s="3">
         <v>9300</v>
       </c>
       <c r="S81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T81" s="3">
         <v>11600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>22400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6373,8 +6568,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,34 +6603,35 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
@@ -6444,10 +6643,10 @@
         <v>700</v>
       </c>
       <c r="O83" s="3">
+        <v>700</v>
+      </c>
+      <c r="P83" s="3">
         <v>800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>700</v>
       </c>
       <c r="Q83" s="3">
         <v>700</v>
@@ -6456,32 +6655,32 @@
         <v>700</v>
       </c>
       <c r="S83" s="3">
+        <v>700</v>
+      </c>
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2400</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6491,8 +6690,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6577,8 +6779,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6663,8 +6868,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6749,8 +6957,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6835,8 +7046,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6921,83 +7135,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>14000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3">
         <v>5700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3">
         <v>4600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>21400</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7007,8 +7224,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,83 +7259,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-700</v>
       </c>
       <c r="J91" s="3">
         <v>-700</v>
       </c>
       <c r="K91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7125,8 +7346,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7211,8 +7435,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7297,83 +7524,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>30500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>9800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>8500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>9800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>13700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3">
         <v>2000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>12700</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7383,8 +7613,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,65 +7648,66 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E96" s="3">
         <v>9100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>9500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>9400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>8600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>10600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>9200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>10800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>8900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>9600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-10400</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-9100</v>
       </c>
       <c r="Q96" s="3">
         <v>-9100</v>
       </c>
       <c r="R96" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="S96" s="3">
         <v>-12100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-10500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-17900</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7501,8 +7735,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7587,8 +7824,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7673,8 +7913,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7759,83 +8002,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-23300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>86100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-22000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>-9700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-27800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7845,83 +8091,86 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7931,83 +8180,86 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E102" s="3">
         <v>11600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-50300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>98100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
         <v>-2100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>17800</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8015,6 +8267,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
